--- a/data/raw/manual_data.xlsx
+++ b/data/raw/manual_data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mpinz-my.sharepoint.com/personal/federico_duranovich_mpi_govt_nz/Documents/Documents/Projects/R projects/autosopi/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_0A9A19B280FD5BAD86A44A52F313CA729B8CB82B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F03F3676-44EF-45B1-9B5B-ECA81C9FF645}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_0A9A19B280FD5BAD86A44A52F313CA729B8CB82B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{370B21F5-9EAA-4046-9096-CF0FF8379437}"/>
   <bookViews>
-    <workbookView xWindow="13560" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13560" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kiwifruit_fig_1" sheetId="1" r:id="rId1"/>
     <sheet name="seafood_fig_1" sheetId="2" r:id="rId2"/>
+    <sheet name="seafood_fig_2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="18">
   <si>
     <t>category</t>
   </si>
@@ -86,11 +87,17 @@
   <si>
     <t>volume</t>
   </si>
+  <si>
+    <t>date</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy/mm/dd;@"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -128,11 +135,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3318,4 +3326,5127 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E91EADBE-6492-438E-AA78-C3168BDFC74A}">
+  <dimension ref="A1:D365"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>34230229</v>
+      </c>
+      <c r="C2">
+        <v>2766237.4920000001</v>
+      </c>
+      <c r="D2" s="2">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>36776111</v>
+      </c>
+      <c r="C3">
+        <v>3011752.1409999998</v>
+      </c>
+      <c r="D3" s="2">
+        <v>44593</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>42998897</v>
+      </c>
+      <c r="C4">
+        <v>3483109.6860000002</v>
+      </c>
+      <c r="D4" s="2">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>28003041</v>
+      </c>
+      <c r="C5">
+        <v>2381906.0729999999</v>
+      </c>
+      <c r="D5" s="2">
+        <v>44652</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>39971024</v>
+      </c>
+      <c r="C6">
+        <v>2881041.4539999999</v>
+      </c>
+      <c r="D6" s="2">
+        <v>44682</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>39371842</v>
+      </c>
+      <c r="C7">
+        <v>3060390.3670000001</v>
+      </c>
+      <c r="D7" s="2">
+        <v>44713</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>38917478</v>
+      </c>
+      <c r="C8">
+        <v>2821346.97</v>
+      </c>
+      <c r="D8" s="2">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>39147020</v>
+      </c>
+      <c r="C9">
+        <v>2759915.841</v>
+      </c>
+      <c r="D9" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>36205267</v>
+      </c>
+      <c r="C10">
+        <v>2514752.2609999999</v>
+      </c>
+      <c r="D10" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>33064892</v>
+      </c>
+      <c r="C11">
+        <v>2053633.727</v>
+      </c>
+      <c r="D11" s="2">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>43168428</v>
+      </c>
+      <c r="C12">
+        <v>2862167.1285999999</v>
+      </c>
+      <c r="D12" s="2">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>53162539</v>
+      </c>
+      <c r="C13">
+        <v>3816563.4580000001</v>
+      </c>
+      <c r="D13" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>36778681</v>
+      </c>
+      <c r="C14">
+        <v>2219877.1660000002</v>
+      </c>
+      <c r="D14" s="2">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>45711995</v>
+      </c>
+      <c r="C15">
+        <v>3477518.568</v>
+      </c>
+      <c r="D15" s="2">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16">
+        <v>51924279</v>
+      </c>
+      <c r="C16">
+        <v>3803621.1779999998</v>
+      </c>
+      <c r="D16" s="2">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>49668422</v>
+      </c>
+      <c r="C17">
+        <v>3469336.2480000001</v>
+      </c>
+      <c r="D17" s="2">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>54930116</v>
+      </c>
+      <c r="C18">
+        <v>4031496.5010000002</v>
+      </c>
+      <c r="D18" s="2">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19">
+        <v>45370036</v>
+      </c>
+      <c r="C19">
+        <v>3086041.01</v>
+      </c>
+      <c r="D19" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20">
+        <v>54188392</v>
+      </c>
+      <c r="C20">
+        <v>3809845.9509999999</v>
+      </c>
+      <c r="D20" s="2">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21">
+        <v>49110571</v>
+      </c>
+      <c r="C21">
+        <v>3084507.2769999998</v>
+      </c>
+      <c r="D21" s="2">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>37436849</v>
+      </c>
+      <c r="C22">
+        <v>2155933.8050000002</v>
+      </c>
+      <c r="D22" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <v>38636901</v>
+      </c>
+      <c r="C23">
+        <v>1978153.888</v>
+      </c>
+      <c r="D23" s="2">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24">
+        <v>54406266</v>
+      </c>
+      <c r="C24">
+        <v>3355473.415</v>
+      </c>
+      <c r="D24" s="2">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25">
+        <v>52257394</v>
+      </c>
+      <c r="C25">
+        <v>3358086.5950000002</v>
+      </c>
+      <c r="D25" s="2">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26">
+        <v>34551329</v>
+      </c>
+      <c r="C26">
+        <v>1875433.93</v>
+      </c>
+      <c r="D26" s="2">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27">
+        <v>44265419</v>
+      </c>
+      <c r="C27">
+        <v>2695434.0559999999</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28">
+        <v>50356001</v>
+      </c>
+      <c r="C28">
+        <v>3243080.7340000002</v>
+      </c>
+      <c r="D28" s="2">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29">
+        <v>45404364</v>
+      </c>
+      <c r="C29">
+        <v>2733476.8560000001</v>
+      </c>
+      <c r="D29" s="2">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30">
+        <v>54536493</v>
+      </c>
+      <c r="C30">
+        <v>3189785.8709999998</v>
+      </c>
+      <c r="D30" s="2">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>57811180</v>
+      </c>
+      <c r="C31">
+        <v>3721005.9730000002</v>
+      </c>
+      <c r="D31" s="2">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32">
+        <v>52212454</v>
+      </c>
+      <c r="C32">
+        <v>3099772.4929999998</v>
+      </c>
+      <c r="D32" s="2">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <v>50743905</v>
+      </c>
+      <c r="C33">
+        <v>2753073.1140000001</v>
+      </c>
+      <c r="D33" s="2">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <v>42246417</v>
+      </c>
+      <c r="C34">
+        <v>2308636.2820000001</v>
+      </c>
+      <c r="D34" s="2">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>48890137</v>
+      </c>
+      <c r="C35">
+        <v>2816119.3939999999</v>
+      </c>
+      <c r="D35" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>59909069</v>
+      </c>
+      <c r="C36">
+        <v>3624374.8280000002</v>
+      </c>
+      <c r="D36" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37">
+        <v>59130515</v>
+      </c>
+      <c r="C37">
+        <v>3644634.8169999998</v>
+      </c>
+      <c r="D37" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38">
+        <v>55725914</v>
+      </c>
+      <c r="C38">
+        <v>2937225.1039999998</v>
+      </c>
+      <c r="D38" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39">
+        <v>60629795</v>
+      </c>
+      <c r="C39">
+        <v>3503875.4840000002</v>
+      </c>
+      <c r="D39" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40">
+        <v>56577097</v>
+      </c>
+      <c r="C40">
+        <v>3359251.59</v>
+      </c>
+      <c r="D40" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41">
+        <v>58069250</v>
+      </c>
+      <c r="C41">
+        <v>3626026.3190000001</v>
+      </c>
+      <c r="D41" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42">
+        <v>65721694</v>
+      </c>
+      <c r="C42">
+        <v>3930516.7050000001</v>
+      </c>
+      <c r="D42" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43">
+        <v>45630833</v>
+      </c>
+      <c r="C43">
+        <v>2982182.3450000002</v>
+      </c>
+      <c r="D43" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44">
+        <v>49595998</v>
+      </c>
+      <c r="C44">
+        <v>3454989.54</v>
+      </c>
+      <c r="D44" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45">
+        <v>50839955</v>
+      </c>
+      <c r="C45">
+        <v>2882280.605</v>
+      </c>
+      <c r="D45" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46">
+        <v>35942941</v>
+      </c>
+      <c r="C46">
+        <v>2203651.3160000001</v>
+      </c>
+      <c r="D46" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47">
+        <v>46799184</v>
+      </c>
+      <c r="C47">
+        <v>2736652.1770000001</v>
+      </c>
+      <c r="D47" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48">
+        <v>56550035</v>
+      </c>
+      <c r="C48">
+        <v>2764214.3459999999</v>
+      </c>
+      <c r="D48" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49">
+        <v>54764976</v>
+      </c>
+      <c r="C49">
+        <v>3447004.298</v>
+      </c>
+      <c r="D49" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50">
+        <v>39874270</v>
+      </c>
+      <c r="C50">
+        <v>2161111.0109999999</v>
+      </c>
+      <c r="D50" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51">
+        <v>44808975</v>
+      </c>
+      <c r="C51">
+        <v>2930709.9870000002</v>
+      </c>
+      <c r="D51" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52">
+        <v>47553519</v>
+      </c>
+      <c r="C52">
+        <v>3063987.74</v>
+      </c>
+      <c r="D52" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53">
+        <v>51043704</v>
+      </c>
+      <c r="C53">
+        <v>3248794.6830000002</v>
+      </c>
+      <c r="D53" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54">
+        <v>40914139</v>
+      </c>
+      <c r="C54">
+        <v>7886083.7740000002</v>
+      </c>
+      <c r="D54" s="2">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55">
+        <v>45575641</v>
+      </c>
+      <c r="C55">
+        <v>9861582.0399999991</v>
+      </c>
+      <c r="D55" s="2">
+        <v>44593</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>79939581</v>
+      </c>
+      <c r="C56">
+        <v>13023997.706</v>
+      </c>
+      <c r="D56" s="2">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57">
+        <v>73159281</v>
+      </c>
+      <c r="C57">
+        <v>15857521.913000001</v>
+      </c>
+      <c r="D57" s="2">
+        <v>44652</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58">
+        <v>71826755</v>
+      </c>
+      <c r="C58">
+        <v>14501912.321</v>
+      </c>
+      <c r="D58" s="2">
+        <v>44682</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59">
+        <v>66145527</v>
+      </c>
+      <c r="C59">
+        <v>11190833.165999999</v>
+      </c>
+      <c r="D59" s="2">
+        <v>44713</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>8</v>
+      </c>
+      <c r="B60">
+        <v>65371658</v>
+      </c>
+      <c r="C60">
+        <v>11665939.443</v>
+      </c>
+      <c r="D60" s="2">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61">
+        <v>56748071</v>
+      </c>
+      <c r="C61">
+        <v>10807010.35</v>
+      </c>
+      <c r="D61" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62">
+        <v>74919349</v>
+      </c>
+      <c r="C62">
+        <v>13993387.346999999</v>
+      </c>
+      <c r="D62" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63">
+        <v>81351260</v>
+      </c>
+      <c r="C63">
+        <v>15423920.035</v>
+      </c>
+      <c r="D63" s="2">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64">
+        <v>64490439</v>
+      </c>
+      <c r="C64">
+        <v>12666931.575999999</v>
+      </c>
+      <c r="D64" s="2">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65">
+        <v>55187530</v>
+      </c>
+      <c r="C65">
+        <v>12258389.060000001</v>
+      </c>
+      <c r="D65" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66">
+        <v>36385701</v>
+      </c>
+      <c r="C66">
+        <v>9858534.693</v>
+      </c>
+      <c r="D66" s="2">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67">
+        <v>46656064</v>
+      </c>
+      <c r="C67">
+        <v>10115438.186000001</v>
+      </c>
+      <c r="D67" s="2">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68">
+        <v>66867108</v>
+      </c>
+      <c r="C68">
+        <v>12920132.578</v>
+      </c>
+      <c r="D68" s="2">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69">
+        <v>74364512</v>
+      </c>
+      <c r="C69">
+        <v>14171766.844000001</v>
+      </c>
+      <c r="D69" s="2">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70">
+        <v>65900321</v>
+      </c>
+      <c r="C70">
+        <v>11157738.543</v>
+      </c>
+      <c r="D70" s="2">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>8</v>
+      </c>
+      <c r="B71">
+        <v>49726128</v>
+      </c>
+      <c r="C71">
+        <v>9900904.2709999997</v>
+      </c>
+      <c r="D71" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>8</v>
+      </c>
+      <c r="B72">
+        <v>48782253</v>
+      </c>
+      <c r="C72">
+        <v>9093342.5010000002</v>
+      </c>
+      <c r="D72" s="2">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73">
+        <v>53122460</v>
+      </c>
+      <c r="C73">
+        <v>11231417.091</v>
+      </c>
+      <c r="D73" s="2">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>8</v>
+      </c>
+      <c r="B74">
+        <v>92814140</v>
+      </c>
+      <c r="C74">
+        <v>18113822.493000001</v>
+      </c>
+      <c r="D74" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75">
+        <v>69316280</v>
+      </c>
+      <c r="C75">
+        <v>12984236.412</v>
+      </c>
+      <c r="D75" s="2">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>8</v>
+      </c>
+      <c r="B76">
+        <v>55535008</v>
+      </c>
+      <c r="C76">
+        <v>12199814.067</v>
+      </c>
+      <c r="D76" s="2">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>8</v>
+      </c>
+      <c r="B77">
+        <v>51528819</v>
+      </c>
+      <c r="C77">
+        <v>12301044.629000001</v>
+      </c>
+      <c r="D77" s="2">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>8</v>
+      </c>
+      <c r="B78">
+        <v>47265776</v>
+      </c>
+      <c r="C78">
+        <v>10690697.544</v>
+      </c>
+      <c r="D78" s="2">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>8</v>
+      </c>
+      <c r="B79">
+        <v>54113892</v>
+      </c>
+      <c r="C79">
+        <v>11737091.287</v>
+      </c>
+      <c r="D79" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>8</v>
+      </c>
+      <c r="B80">
+        <v>85869881</v>
+      </c>
+      <c r="C80">
+        <v>17389897.526999999</v>
+      </c>
+      <c r="D80" s="2">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81">
+        <v>70671900</v>
+      </c>
+      <c r="C81">
+        <v>13616310.766000001</v>
+      </c>
+      <c r="D81" s="2">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82">
+        <v>72574145</v>
+      </c>
+      <c r="C82">
+        <v>11393040.75</v>
+      </c>
+      <c r="D82" s="2">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83">
+        <v>57913257</v>
+      </c>
+      <c r="C83">
+        <v>9149657.125</v>
+      </c>
+      <c r="D83" s="2">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84">
+        <v>64984478</v>
+      </c>
+      <c r="C84">
+        <v>9566281.0179999992</v>
+      </c>
+      <c r="D84" s="2">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85">
+        <v>71976408</v>
+      </c>
+      <c r="C85">
+        <v>12852635.767999999</v>
+      </c>
+      <c r="D85" s="2">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86">
+        <v>91824879</v>
+      </c>
+      <c r="C86">
+        <v>15967138.002</v>
+      </c>
+      <c r="D86" s="2">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87">
+        <v>60164179</v>
+      </c>
+      <c r="C87">
+        <v>11237017.659</v>
+      </c>
+      <c r="D87" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88">
+        <v>62808615</v>
+      </c>
+      <c r="C88">
+        <v>13439577.717</v>
+      </c>
+      <c r="D88" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89">
+        <v>73527862</v>
+      </c>
+      <c r="C89">
+        <v>14566174.477</v>
+      </c>
+      <c r="D89" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90">
+        <v>54553784</v>
+      </c>
+      <c r="C90">
+        <v>10499424.412</v>
+      </c>
+      <c r="D90" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91">
+        <v>61442400</v>
+      </c>
+      <c r="C91">
+        <v>13436351.628</v>
+      </c>
+      <c r="D91" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92">
+        <v>78666948</v>
+      </c>
+      <c r="C92">
+        <v>14861113.835000001</v>
+      </c>
+      <c r="D92" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93">
+        <v>91171899</v>
+      </c>
+      <c r="C93">
+        <v>14805546.107000001</v>
+      </c>
+      <c r="D93" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94">
+        <v>69536148</v>
+      </c>
+      <c r="C94">
+        <v>11093727.455</v>
+      </c>
+      <c r="D94" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95">
+        <v>69008904</v>
+      </c>
+      <c r="C95">
+        <v>10475360.43</v>
+      </c>
+      <c r="D95" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96">
+        <v>76847343</v>
+      </c>
+      <c r="C96">
+        <v>11443497.264</v>
+      </c>
+      <c r="D96" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97">
+        <v>89517064</v>
+      </c>
+      <c r="C97">
+        <v>11526795.596000001</v>
+      </c>
+      <c r="D97" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98">
+        <v>76457312</v>
+      </c>
+      <c r="C98">
+        <v>12020304.466</v>
+      </c>
+      <c r="D98" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99">
+        <v>72478870</v>
+      </c>
+      <c r="C99">
+        <v>13465095.877</v>
+      </c>
+      <c r="D99" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100">
+        <v>72966771</v>
+      </c>
+      <c r="C100">
+        <v>15143556.41</v>
+      </c>
+      <c r="D100" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101">
+        <v>99089122</v>
+      </c>
+      <c r="C101">
+        <v>16621081.492000001</v>
+      </c>
+      <c r="D101" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102">
+        <v>54064657</v>
+      </c>
+      <c r="C102">
+        <v>9341636.5559999999</v>
+      </c>
+      <c r="D102" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103">
+        <v>73660520</v>
+      </c>
+      <c r="C103">
+        <v>13276874.550000001</v>
+      </c>
+      <c r="D103" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104">
+        <v>90260225</v>
+      </c>
+      <c r="C104">
+        <v>14147118.290999999</v>
+      </c>
+      <c r="D104" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105">
+        <v>100140559</v>
+      </c>
+      <c r="C105">
+        <v>12906282.364</v>
+      </c>
+      <c r="D105" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106">
+        <v>280252</v>
+      </c>
+      <c r="C106">
+        <v>12910.504000000001</v>
+      </c>
+      <c r="D106" s="2">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107">
+        <v>352534</v>
+      </c>
+      <c r="C107">
+        <v>31460.066999999999</v>
+      </c>
+      <c r="D107" s="2">
+        <v>44593</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B108">
+        <v>98176</v>
+      </c>
+      <c r="C108">
+        <v>6080.7619999999997</v>
+      </c>
+      <c r="D108" s="2">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B109">
+        <v>98254</v>
+      </c>
+      <c r="C109">
+        <v>6879.7020000000002</v>
+      </c>
+      <c r="D109" s="2">
+        <v>44652</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B110">
+        <v>125897</v>
+      </c>
+      <c r="C110">
+        <v>11306.955</v>
+      </c>
+      <c r="D110" s="2">
+        <v>44682</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>9</v>
+      </c>
+      <c r="B111">
+        <v>157958</v>
+      </c>
+      <c r="C111">
+        <v>10294.659</v>
+      </c>
+      <c r="D111" s="2">
+        <v>44713</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>9</v>
+      </c>
+      <c r="B112">
+        <v>719785</v>
+      </c>
+      <c r="C112">
+        <v>62855.008999999998</v>
+      </c>
+      <c r="D112" s="2">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>9</v>
+      </c>
+      <c r="B113">
+        <v>162192</v>
+      </c>
+      <c r="C113">
+        <v>9475.36</v>
+      </c>
+      <c r="D113" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>9</v>
+      </c>
+      <c r="B114">
+        <v>285940</v>
+      </c>
+      <c r="C114">
+        <v>17542.535</v>
+      </c>
+      <c r="D114" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>9</v>
+      </c>
+      <c r="B115">
+        <v>492040</v>
+      </c>
+      <c r="C115">
+        <v>25578.874</v>
+      </c>
+      <c r="D115" s="2">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116">
+        <v>312219</v>
+      </c>
+      <c r="C116">
+        <v>16025.028</v>
+      </c>
+      <c r="D116" s="2">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>9</v>
+      </c>
+      <c r="B117">
+        <v>210842</v>
+      </c>
+      <c r="C117">
+        <v>13737.112999999999</v>
+      </c>
+      <c r="D117" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>9</v>
+      </c>
+      <c r="B118">
+        <v>102577</v>
+      </c>
+      <c r="C118">
+        <v>6065.0069999999996</v>
+      </c>
+      <c r="D118" s="2">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>9</v>
+      </c>
+      <c r="B119">
+        <v>122725</v>
+      </c>
+      <c r="C119">
+        <v>7665.2619999999997</v>
+      </c>
+      <c r="D119" s="2">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>9</v>
+      </c>
+      <c r="B120">
+        <v>227127</v>
+      </c>
+      <c r="C120">
+        <v>15503.036</v>
+      </c>
+      <c r="D120" s="2">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>9</v>
+      </c>
+      <c r="B121">
+        <v>337428</v>
+      </c>
+      <c r="C121">
+        <v>23429</v>
+      </c>
+      <c r="D121" s="2">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>9</v>
+      </c>
+      <c r="B122">
+        <v>317163</v>
+      </c>
+      <c r="C122">
+        <v>32501.554</v>
+      </c>
+      <c r="D122" s="2">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>9</v>
+      </c>
+      <c r="B123">
+        <v>278127</v>
+      </c>
+      <c r="C123">
+        <v>33994.285000000003</v>
+      </c>
+      <c r="D123" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>9</v>
+      </c>
+      <c r="B124">
+        <v>457013</v>
+      </c>
+      <c r="C124">
+        <v>82925.214999999997</v>
+      </c>
+      <c r="D124" s="2">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>9</v>
+      </c>
+      <c r="B125">
+        <v>261357</v>
+      </c>
+      <c r="C125">
+        <v>13503.01</v>
+      </c>
+      <c r="D125" s="2">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>9</v>
+      </c>
+      <c r="B126">
+        <v>439925</v>
+      </c>
+      <c r="C126">
+        <v>23593</v>
+      </c>
+      <c r="D126" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>9</v>
+      </c>
+      <c r="B127">
+        <v>317568</v>
+      </c>
+      <c r="C127">
+        <v>58455.656999999999</v>
+      </c>
+      <c r="D127" s="2">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128">
+        <v>583437</v>
+      </c>
+      <c r="C128">
+        <v>91989.38</v>
+      </c>
+      <c r="D128" s="2">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129">
+        <v>140179</v>
+      </c>
+      <c r="C129">
+        <v>8178.0050000000001</v>
+      </c>
+      <c r="D129" s="2">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>9</v>
+      </c>
+      <c r="B130">
+        <v>373267</v>
+      </c>
+      <c r="C130">
+        <v>18829.005000000001</v>
+      </c>
+      <c r="D130" s="2">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131">
+        <v>288963</v>
+      </c>
+      <c r="C131">
+        <v>17659.016</v>
+      </c>
+      <c r="D131" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132">
+        <v>283402</v>
+      </c>
+      <c r="C132">
+        <v>19877.009999999998</v>
+      </c>
+      <c r="D132" s="2">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133">
+        <v>506825</v>
+      </c>
+      <c r="C133">
+        <v>29242.235000000001</v>
+      </c>
+      <c r="D133" s="2">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134">
+        <v>232482</v>
+      </c>
+      <c r="C134">
+        <v>14449.15</v>
+      </c>
+      <c r="D134" s="2">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135">
+        <v>299576</v>
+      </c>
+      <c r="C135">
+        <v>43741.004999999997</v>
+      </c>
+      <c r="D135" s="2">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>9</v>
+      </c>
+      <c r="B136">
+        <v>237252</v>
+      </c>
+      <c r="C136">
+        <v>28126.023000000001</v>
+      </c>
+      <c r="D136" s="2">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137">
+        <v>455586</v>
+      </c>
+      <c r="C137">
+        <v>23013.496999999999</v>
+      </c>
+      <c r="D137" s="2">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138">
+        <v>367657</v>
+      </c>
+      <c r="C138">
+        <v>26795.985000000001</v>
+      </c>
+      <c r="D138" s="2">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139">
+        <v>328123</v>
+      </c>
+      <c r="C139">
+        <v>21598</v>
+      </c>
+      <c r="D139" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140">
+        <v>232402</v>
+      </c>
+      <c r="C140">
+        <v>12975.405000000001</v>
+      </c>
+      <c r="D140" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141">
+        <v>932104</v>
+      </c>
+      <c r="C141">
+        <v>53818.506999999998</v>
+      </c>
+      <c r="D141" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142">
+        <v>172058</v>
+      </c>
+      <c r="C142">
+        <v>8822.0049999999992</v>
+      </c>
+      <c r="D142" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143">
+        <v>570852</v>
+      </c>
+      <c r="C143">
+        <v>39828.815999999999</v>
+      </c>
+      <c r="D143" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144">
+        <v>312896</v>
+      </c>
+      <c r="C144">
+        <v>17315.036</v>
+      </c>
+      <c r="D144" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145">
+        <v>424392</v>
+      </c>
+      <c r="C145">
+        <v>42042.035000000003</v>
+      </c>
+      <c r="D145" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146">
+        <v>542214</v>
+      </c>
+      <c r="C146">
+        <v>34827.023000000001</v>
+      </c>
+      <c r="D146" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147">
+        <v>248018</v>
+      </c>
+      <c r="C147">
+        <v>13361.037</v>
+      </c>
+      <c r="D147" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148">
+        <v>270111</v>
+      </c>
+      <c r="C148">
+        <v>31138.01</v>
+      </c>
+      <c r="D148" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149">
+        <v>203399</v>
+      </c>
+      <c r="C149">
+        <v>12099.763000000001</v>
+      </c>
+      <c r="D149" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150">
+        <v>735061</v>
+      </c>
+      <c r="C150">
+        <v>55374.644999999997</v>
+      </c>
+      <c r="D150" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151">
+        <v>630688</v>
+      </c>
+      <c r="C151">
+        <v>45130.025999999998</v>
+      </c>
+      <c r="D151" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152">
+        <v>192746</v>
+      </c>
+      <c r="C152">
+        <v>24943.014999999999</v>
+      </c>
+      <c r="D152" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153">
+        <v>1345608</v>
+      </c>
+      <c r="C153">
+        <v>70911.027000000002</v>
+      </c>
+      <c r="D153" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>9</v>
+      </c>
+      <c r="B154">
+        <v>227078</v>
+      </c>
+      <c r="C154">
+        <v>33316.025999999998</v>
+      </c>
+      <c r="D154" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>9</v>
+      </c>
+      <c r="B155">
+        <v>245516</v>
+      </c>
+      <c r="C155">
+        <v>14333.691000000001</v>
+      </c>
+      <c r="D155" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156">
+        <v>651274</v>
+      </c>
+      <c r="C156">
+        <v>29746.471000000001</v>
+      </c>
+      <c r="D156" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>9</v>
+      </c>
+      <c r="B157">
+        <v>468895</v>
+      </c>
+      <c r="C157">
+        <v>26192.431</v>
+      </c>
+      <c r="D157" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>10</v>
+      </c>
+      <c r="B158">
+        <v>7350384</v>
+      </c>
+      <c r="C158">
+        <v>1076421.9010000001</v>
+      </c>
+      <c r="D158" s="2">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>10</v>
+      </c>
+      <c r="B159">
+        <v>8786819</v>
+      </c>
+      <c r="C159">
+        <v>1341883.3470000001</v>
+      </c>
+      <c r="D159" s="2">
+        <v>44593</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>10</v>
+      </c>
+      <c r="B160">
+        <v>8102372</v>
+      </c>
+      <c r="C160">
+        <v>1001664.868</v>
+      </c>
+      <c r="D160" s="2">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>10</v>
+      </c>
+      <c r="B161">
+        <v>8455584</v>
+      </c>
+      <c r="C161">
+        <v>969168.72</v>
+      </c>
+      <c r="D161" s="2">
+        <v>44652</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>10</v>
+      </c>
+      <c r="B162">
+        <v>8753715</v>
+      </c>
+      <c r="C162">
+        <v>1123059.4990999999</v>
+      </c>
+      <c r="D162" s="2">
+        <v>44682</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>10</v>
+      </c>
+      <c r="B163">
+        <v>6664746</v>
+      </c>
+      <c r="C163">
+        <v>740657.81400000001</v>
+      </c>
+      <c r="D163" s="2">
+        <v>44713</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>10</v>
+      </c>
+      <c r="B164">
+        <v>7804626</v>
+      </c>
+      <c r="C164">
+        <v>1103803.1629999999</v>
+      </c>
+      <c r="D164" s="2">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>10</v>
+      </c>
+      <c r="B165">
+        <v>8317346</v>
+      </c>
+      <c r="C165">
+        <v>1037291.28</v>
+      </c>
+      <c r="D165" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>10</v>
+      </c>
+      <c r="B166">
+        <v>8931739</v>
+      </c>
+      <c r="C166">
+        <v>957810.76</v>
+      </c>
+      <c r="D166" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167">
+        <v>9374883</v>
+      </c>
+      <c r="C167">
+        <v>1038949.379</v>
+      </c>
+      <c r="D167" s="2">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>10</v>
+      </c>
+      <c r="B168">
+        <v>10131173</v>
+      </c>
+      <c r="C168">
+        <v>1072675.993</v>
+      </c>
+      <c r="D168" s="2">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>10</v>
+      </c>
+      <c r="B169">
+        <v>9302083</v>
+      </c>
+      <c r="C169">
+        <v>1126581.504</v>
+      </c>
+      <c r="D169" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>10</v>
+      </c>
+      <c r="B170">
+        <v>8692168</v>
+      </c>
+      <c r="C170">
+        <v>800713.125</v>
+      </c>
+      <c r="D170" s="2">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>10</v>
+      </c>
+      <c r="B171">
+        <v>9993537</v>
+      </c>
+      <c r="C171">
+        <v>1253344.68</v>
+      </c>
+      <c r="D171" s="2">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>10</v>
+      </c>
+      <c r="B172">
+        <v>10506051</v>
+      </c>
+      <c r="C172">
+        <v>1377498.554</v>
+      </c>
+      <c r="D172" s="2">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>10</v>
+      </c>
+      <c r="B173">
+        <v>10179331</v>
+      </c>
+      <c r="C173">
+        <v>1246772.929</v>
+      </c>
+      <c r="D173" s="2">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>10</v>
+      </c>
+      <c r="B174">
+        <v>8237385</v>
+      </c>
+      <c r="C174">
+        <v>1061489.591</v>
+      </c>
+      <c r="D174" s="2">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>10</v>
+      </c>
+      <c r="B175">
+        <v>7049526</v>
+      </c>
+      <c r="C175">
+        <v>809270.82200000004</v>
+      </c>
+      <c r="D175" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>10</v>
+      </c>
+      <c r="B176">
+        <v>7612178</v>
+      </c>
+      <c r="C176">
+        <v>1033597.526</v>
+      </c>
+      <c r="D176" s="2">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>10</v>
+      </c>
+      <c r="B177">
+        <v>8301079</v>
+      </c>
+      <c r="C177">
+        <v>1121896.3970000001</v>
+      </c>
+      <c r="D177" s="2">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>10</v>
+      </c>
+      <c r="B178">
+        <v>6574345</v>
+      </c>
+      <c r="C178">
+        <v>740805.82400000002</v>
+      </c>
+      <c r="D178" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>10</v>
+      </c>
+      <c r="B179">
+        <v>7913473</v>
+      </c>
+      <c r="C179">
+        <v>818753.43500000006</v>
+      </c>
+      <c r="D179" s="2">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>10</v>
+      </c>
+      <c r="B180">
+        <v>9347685</v>
+      </c>
+      <c r="C180">
+        <v>1036813.7929999999</v>
+      </c>
+      <c r="D180" s="2">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>10</v>
+      </c>
+      <c r="B181">
+        <v>9527433</v>
+      </c>
+      <c r="C181">
+        <v>963600.91399999999</v>
+      </c>
+      <c r="D181" s="2">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>10</v>
+      </c>
+      <c r="B182">
+        <v>8643260</v>
+      </c>
+      <c r="C182">
+        <v>759772.17799999996</v>
+      </c>
+      <c r="D182" s="2">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>10</v>
+      </c>
+      <c r="B183">
+        <v>8945591</v>
+      </c>
+      <c r="C183">
+        <v>890449.06900000002</v>
+      </c>
+      <c r="D183" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>10</v>
+      </c>
+      <c r="B184">
+        <v>8677881</v>
+      </c>
+      <c r="C184">
+        <v>881095.76699999999</v>
+      </c>
+      <c r="D184" s="2">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>10</v>
+      </c>
+      <c r="B185">
+        <v>8020342</v>
+      </c>
+      <c r="C185">
+        <v>806459.18299999996</v>
+      </c>
+      <c r="D185" s="2">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>10</v>
+      </c>
+      <c r="B186">
+        <v>8861119</v>
+      </c>
+      <c r="C186">
+        <v>1052103.348</v>
+      </c>
+      <c r="D186" s="2">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>10</v>
+      </c>
+      <c r="B187">
+        <v>6994105</v>
+      </c>
+      <c r="C187">
+        <v>713639.69700000004</v>
+      </c>
+      <c r="D187" s="2">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>10</v>
+      </c>
+      <c r="B188">
+        <v>7345549</v>
+      </c>
+      <c r="C188">
+        <v>645194.27099999995</v>
+      </c>
+      <c r="D188" s="2">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>10</v>
+      </c>
+      <c r="B189">
+        <v>7245034</v>
+      </c>
+      <c r="C189">
+        <v>787477.55099999998</v>
+      </c>
+      <c r="D189" s="2">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>10</v>
+      </c>
+      <c r="B190">
+        <v>7871493</v>
+      </c>
+      <c r="C190">
+        <v>1000757.165</v>
+      </c>
+      <c r="D190" s="2">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>10</v>
+      </c>
+      <c r="B191">
+        <v>8914775</v>
+      </c>
+      <c r="C191">
+        <v>1081147.591</v>
+      </c>
+      <c r="D191" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>10</v>
+      </c>
+      <c r="B192">
+        <v>10412841</v>
+      </c>
+      <c r="C192">
+        <v>1081997.68</v>
+      </c>
+      <c r="D192" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>10</v>
+      </c>
+      <c r="B193">
+        <v>10533908</v>
+      </c>
+      <c r="C193">
+        <v>970386.60199999996</v>
+      </c>
+      <c r="D193" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>10</v>
+      </c>
+      <c r="B194">
+        <v>9076704</v>
+      </c>
+      <c r="C194">
+        <v>825013.56900000002</v>
+      </c>
+      <c r="D194" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>10</v>
+      </c>
+      <c r="B195">
+        <v>8969643</v>
+      </c>
+      <c r="C195">
+        <v>785408.05099999998</v>
+      </c>
+      <c r="D195" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>10</v>
+      </c>
+      <c r="B196">
+        <v>12137560</v>
+      </c>
+      <c r="C196">
+        <v>1294839.625</v>
+      </c>
+      <c r="D196" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>10</v>
+      </c>
+      <c r="B197">
+        <v>10600749</v>
+      </c>
+      <c r="C197">
+        <v>1250739.871</v>
+      </c>
+      <c r="D197" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>10</v>
+      </c>
+      <c r="B198">
+        <v>9074168</v>
+      </c>
+      <c r="C198">
+        <v>982759.01100000006</v>
+      </c>
+      <c r="D198" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>10</v>
+      </c>
+      <c r="B199">
+        <v>9472099</v>
+      </c>
+      <c r="C199">
+        <v>1402028.611</v>
+      </c>
+      <c r="D199" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>10</v>
+      </c>
+      <c r="B200">
+        <v>8344553</v>
+      </c>
+      <c r="C200">
+        <v>1136673.5090000001</v>
+      </c>
+      <c r="D200" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>10</v>
+      </c>
+      <c r="B201">
+        <v>9542557</v>
+      </c>
+      <c r="C201">
+        <v>1106708.493</v>
+      </c>
+      <c r="D201" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>10</v>
+      </c>
+      <c r="B202">
+        <v>8936830</v>
+      </c>
+      <c r="C202">
+        <v>1080294.8700000001</v>
+      </c>
+      <c r="D202" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>10</v>
+      </c>
+      <c r="B203">
+        <v>10183037</v>
+      </c>
+      <c r="C203">
+        <v>1202125.8729999999</v>
+      </c>
+      <c r="D203" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>10</v>
+      </c>
+      <c r="B204">
+        <v>9763474</v>
+      </c>
+      <c r="C204">
+        <v>1021548.4</v>
+      </c>
+      <c r="D204" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>10</v>
+      </c>
+      <c r="B205">
+        <v>11431604</v>
+      </c>
+      <c r="C205">
+        <v>968660.04200000002</v>
+      </c>
+      <c r="D205" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>10</v>
+      </c>
+      <c r="B206">
+        <v>9884631</v>
+      </c>
+      <c r="C206">
+        <v>856366.73600000003</v>
+      </c>
+      <c r="D206" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>10</v>
+      </c>
+      <c r="B207">
+        <v>10927289</v>
+      </c>
+      <c r="C207">
+        <v>883089.59199999995</v>
+      </c>
+      <c r="D207" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>10</v>
+      </c>
+      <c r="B208">
+        <v>13317609</v>
+      </c>
+      <c r="C208">
+        <v>1311075.615</v>
+      </c>
+      <c r="D208" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>10</v>
+      </c>
+      <c r="B209">
+        <v>10624007</v>
+      </c>
+      <c r="C209">
+        <v>1278946.0220000001</v>
+      </c>
+      <c r="D209" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>11</v>
+      </c>
+      <c r="B210">
+        <v>45967898</v>
+      </c>
+      <c r="C210">
+        <v>471745.03600000002</v>
+      </c>
+      <c r="D210" s="2">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>11</v>
+      </c>
+      <c r="B211">
+        <v>37559008</v>
+      </c>
+      <c r="C211">
+        <v>565208.01599999995</v>
+      </c>
+      <c r="D211" s="2">
+        <v>44593</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>11</v>
+      </c>
+      <c r="B212">
+        <v>11210169</v>
+      </c>
+      <c r="C212">
+        <v>499131.734</v>
+      </c>
+      <c r="D212" s="2">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>11</v>
+      </c>
+      <c r="B213">
+        <v>7150337</v>
+      </c>
+      <c r="C213">
+        <v>173476.36300000001</v>
+      </c>
+      <c r="D213" s="2">
+        <v>44652</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>11</v>
+      </c>
+      <c r="B214">
+        <v>27117836</v>
+      </c>
+      <c r="C214">
+        <v>309013.37099999998</v>
+      </c>
+      <c r="D214" s="2">
+        <v>44682</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>11</v>
+      </c>
+      <c r="B215">
+        <v>33821830</v>
+      </c>
+      <c r="C215">
+        <v>371896.50300000003</v>
+      </c>
+      <c r="D215" s="2">
+        <v>44713</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>11</v>
+      </c>
+      <c r="B216">
+        <v>33246568</v>
+      </c>
+      <c r="C216">
+        <v>373428.17099999997</v>
+      </c>
+      <c r="D216" s="2">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>11</v>
+      </c>
+      <c r="B217">
+        <v>40076086</v>
+      </c>
+      <c r="C217">
+        <v>405980.18699999998</v>
+      </c>
+      <c r="D217" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>11</v>
+      </c>
+      <c r="B218">
+        <v>67217361</v>
+      </c>
+      <c r="C218">
+        <v>558140.99199999997</v>
+      </c>
+      <c r="D218" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>11</v>
+      </c>
+      <c r="B219">
+        <v>49489627</v>
+      </c>
+      <c r="C219">
+        <v>477833.22</v>
+      </c>
+      <c r="D219" s="2">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>11</v>
+      </c>
+      <c r="B220">
+        <v>48948556</v>
+      </c>
+      <c r="C220">
+        <v>512708.78</v>
+      </c>
+      <c r="D220" s="2">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>11</v>
+      </c>
+      <c r="B221">
+        <v>26370928</v>
+      </c>
+      <c r="C221">
+        <v>322230.94199999998</v>
+      </c>
+      <c r="D221" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222">
+        <v>43757108</v>
+      </c>
+      <c r="C222">
+        <v>437362.35100000002</v>
+      </c>
+      <c r="D222" s="2">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>11</v>
+      </c>
+      <c r="B223">
+        <v>33797411</v>
+      </c>
+      <c r="C223">
+        <v>358412.11200000002</v>
+      </c>
+      <c r="D223" s="2">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>11</v>
+      </c>
+      <c r="B224">
+        <v>32068600</v>
+      </c>
+      <c r="C224">
+        <v>379510.81</v>
+      </c>
+      <c r="D224" s="2">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>11</v>
+      </c>
+      <c r="B225">
+        <v>50331022</v>
+      </c>
+      <c r="C225">
+        <v>448249.16499999998</v>
+      </c>
+      <c r="D225" s="2">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>11</v>
+      </c>
+      <c r="B226">
+        <v>53230005</v>
+      </c>
+      <c r="C226">
+        <v>456611.647</v>
+      </c>
+      <c r="D226" s="2">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>11</v>
+      </c>
+      <c r="B227">
+        <v>42608820</v>
+      </c>
+      <c r="C227">
+        <v>456244.95699999999</v>
+      </c>
+      <c r="D227" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>11</v>
+      </c>
+      <c r="B228">
+        <v>32427345</v>
+      </c>
+      <c r="C228">
+        <v>337317.88</v>
+      </c>
+      <c r="D228" s="2">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>11</v>
+      </c>
+      <c r="B229">
+        <v>36204999</v>
+      </c>
+      <c r="C229">
+        <v>365327.21100000001</v>
+      </c>
+      <c r="D229" s="2">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>11</v>
+      </c>
+      <c r="B230">
+        <v>59978256</v>
+      </c>
+      <c r="C230">
+        <v>535790.125</v>
+      </c>
+      <c r="D230" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>11</v>
+      </c>
+      <c r="B231">
+        <v>48187668</v>
+      </c>
+      <c r="C231">
+        <v>465728.67599999998</v>
+      </c>
+      <c r="D231" s="2">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>11</v>
+      </c>
+      <c r="B232">
+        <v>47411983</v>
+      </c>
+      <c r="C232">
+        <v>462811.91600000003</v>
+      </c>
+      <c r="D232" s="2">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>11</v>
+      </c>
+      <c r="B233">
+        <v>38795280</v>
+      </c>
+      <c r="C233">
+        <v>396591.06300000002</v>
+      </c>
+      <c r="D233" s="2">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>11</v>
+      </c>
+      <c r="B234">
+        <v>41556133</v>
+      </c>
+      <c r="C234">
+        <v>352947.31300000002</v>
+      </c>
+      <c r="D234" s="2">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>11</v>
+      </c>
+      <c r="B235">
+        <v>55169357</v>
+      </c>
+      <c r="C235">
+        <v>462632.15700000001</v>
+      </c>
+      <c r="D235" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>11</v>
+      </c>
+      <c r="B236">
+        <v>29979365</v>
+      </c>
+      <c r="C236">
+        <v>318453.43</v>
+      </c>
+      <c r="D236" s="2">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>11</v>
+      </c>
+      <c r="B237">
+        <v>45450752</v>
+      </c>
+      <c r="C237">
+        <v>408994.53899999999</v>
+      </c>
+      <c r="D237" s="2">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>11</v>
+      </c>
+      <c r="B238">
+        <v>45828452</v>
+      </c>
+      <c r="C238">
+        <v>439793.79</v>
+      </c>
+      <c r="D238" s="2">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>11</v>
+      </c>
+      <c r="B239">
+        <v>29480302</v>
+      </c>
+      <c r="C239">
+        <v>293458.28000000003</v>
+      </c>
+      <c r="D239" s="2">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>11</v>
+      </c>
+      <c r="B240">
+        <v>31668906</v>
+      </c>
+      <c r="C240">
+        <v>366438.86</v>
+      </c>
+      <c r="D240" s="2">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>11</v>
+      </c>
+      <c r="B241">
+        <v>27498438</v>
+      </c>
+      <c r="C241">
+        <v>348035.53200000001</v>
+      </c>
+      <c r="D241" s="2">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>11</v>
+      </c>
+      <c r="B242">
+        <v>49063403</v>
+      </c>
+      <c r="C242">
+        <v>515849.90700000001</v>
+      </c>
+      <c r="D242" s="2">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>11</v>
+      </c>
+      <c r="B243">
+        <v>34936257</v>
+      </c>
+      <c r="C243">
+        <v>333075.71000000002</v>
+      </c>
+      <c r="D243" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>11</v>
+      </c>
+      <c r="B244">
+        <v>52521476</v>
+      </c>
+      <c r="C244">
+        <v>507444.7</v>
+      </c>
+      <c r="D244" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>11</v>
+      </c>
+      <c r="B245">
+        <v>31236672</v>
+      </c>
+      <c r="C245">
+        <v>366831.12599999999</v>
+      </c>
+      <c r="D245" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>11</v>
+      </c>
+      <c r="B246">
+        <v>33753722</v>
+      </c>
+      <c r="C246">
+        <v>426432.76899999997</v>
+      </c>
+      <c r="D246" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>11</v>
+      </c>
+      <c r="B247">
+        <v>34704302</v>
+      </c>
+      <c r="C247">
+        <v>460745.12400000001</v>
+      </c>
+      <c r="D247" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>11</v>
+      </c>
+      <c r="B248">
+        <v>19180362</v>
+      </c>
+      <c r="C248">
+        <v>330080.864</v>
+      </c>
+      <c r="D248" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>11</v>
+      </c>
+      <c r="B249">
+        <v>29308210</v>
+      </c>
+      <c r="C249">
+        <v>328266.38500000001</v>
+      </c>
+      <c r="D249" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>11</v>
+      </c>
+      <c r="B250">
+        <v>34378348</v>
+      </c>
+      <c r="C250">
+        <v>335665.02600000001</v>
+      </c>
+      <c r="D250" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>11</v>
+      </c>
+      <c r="B251">
+        <v>26150340</v>
+      </c>
+      <c r="C251">
+        <v>308856.62</v>
+      </c>
+      <c r="D251" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>11</v>
+      </c>
+      <c r="B252">
+        <v>20930981</v>
+      </c>
+      <c r="C252">
+        <v>342389.93900000001</v>
+      </c>
+      <c r="D252" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>11</v>
+      </c>
+      <c r="B253">
+        <v>20534681</v>
+      </c>
+      <c r="C253">
+        <v>309267.13</v>
+      </c>
+      <c r="D253" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>11</v>
+      </c>
+      <c r="B254">
+        <v>27874477</v>
+      </c>
+      <c r="C254">
+        <v>379607.51199999999</v>
+      </c>
+      <c r="D254" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>11</v>
+      </c>
+      <c r="B255">
+        <v>29561583</v>
+      </c>
+      <c r="C255">
+        <v>341346.55599999998</v>
+      </c>
+      <c r="D255" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>11</v>
+      </c>
+      <c r="B256">
+        <v>31837095</v>
+      </c>
+      <c r="C256">
+        <v>379357.82900000003</v>
+      </c>
+      <c r="D256" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>11</v>
+      </c>
+      <c r="B257">
+        <v>28980014</v>
+      </c>
+      <c r="C257">
+        <v>371579.25300000003</v>
+      </c>
+      <c r="D257" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>11</v>
+      </c>
+      <c r="B258">
+        <v>29615211</v>
+      </c>
+      <c r="C258">
+        <v>344816.55</v>
+      </c>
+      <c r="D258" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>11</v>
+      </c>
+      <c r="B259">
+        <v>37802842</v>
+      </c>
+      <c r="C259">
+        <v>390326.77</v>
+      </c>
+      <c r="D259" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>11</v>
+      </c>
+      <c r="B260">
+        <v>18919266</v>
+      </c>
+      <c r="C260">
+        <v>271799.00099999999</v>
+      </c>
+      <c r="D260" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>11</v>
+      </c>
+      <c r="B261">
+        <v>36653386</v>
+      </c>
+      <c r="C261">
+        <v>315752.8</v>
+      </c>
+      <c r="D261" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>12</v>
+      </c>
+      <c r="B262">
+        <v>8049956</v>
+      </c>
+      <c r="C262">
+        <v>1781689.9350000001</v>
+      </c>
+      <c r="D262" s="2">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>12</v>
+      </c>
+      <c r="B263">
+        <v>11141505</v>
+      </c>
+      <c r="C263">
+        <v>2297866.923</v>
+      </c>
+      <c r="D263" s="2">
+        <v>44593</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>12</v>
+      </c>
+      <c r="B264">
+        <v>15005482</v>
+      </c>
+      <c r="C264">
+        <v>2886880.0150000001</v>
+      </c>
+      <c r="D264" s="2">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>12</v>
+      </c>
+      <c r="B265">
+        <v>16732028</v>
+      </c>
+      <c r="C265">
+        <v>2956096.8059999999</v>
+      </c>
+      <c r="D265" s="2">
+        <v>44652</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>12</v>
+      </c>
+      <c r="B266">
+        <v>10759887</v>
+      </c>
+      <c r="C266">
+        <v>2066360.409</v>
+      </c>
+      <c r="D266" s="2">
+        <v>44682</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>12</v>
+      </c>
+      <c r="B267">
+        <v>10477646</v>
+      </c>
+      <c r="C267">
+        <v>2022016.1510000001</v>
+      </c>
+      <c r="D267" s="2">
+        <v>44713</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>12</v>
+      </c>
+      <c r="B268">
+        <v>12842881</v>
+      </c>
+      <c r="C268">
+        <v>2382189.9810000001</v>
+      </c>
+      <c r="D268" s="2">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>12</v>
+      </c>
+      <c r="B269">
+        <v>14513762</v>
+      </c>
+      <c r="C269">
+        <v>2389450.27</v>
+      </c>
+      <c r="D269" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>12</v>
+      </c>
+      <c r="B270">
+        <v>18452180</v>
+      </c>
+      <c r="C270">
+        <v>3145775.0490000001</v>
+      </c>
+      <c r="D270" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>12</v>
+      </c>
+      <c r="B271">
+        <v>18884144</v>
+      </c>
+      <c r="C271">
+        <v>3059110.35</v>
+      </c>
+      <c r="D271" s="2">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>12</v>
+      </c>
+      <c r="B272">
+        <v>18368217</v>
+      </c>
+      <c r="C272">
+        <v>2549835.7719999999</v>
+      </c>
+      <c r="D272" s="2">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>12</v>
+      </c>
+      <c r="B273">
+        <v>12832673</v>
+      </c>
+      <c r="C273">
+        <v>2432350.41</v>
+      </c>
+      <c r="D273" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>12</v>
+      </c>
+      <c r="B274">
+        <v>11787358</v>
+      </c>
+      <c r="C274">
+        <v>1799008.916</v>
+      </c>
+      <c r="D274" s="2">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>12</v>
+      </c>
+      <c r="B275">
+        <v>9823704</v>
+      </c>
+      <c r="C275">
+        <v>1949772.301</v>
+      </c>
+      <c r="D275" s="2">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>12</v>
+      </c>
+      <c r="B276">
+        <v>15273471</v>
+      </c>
+      <c r="C276">
+        <v>3333364.7960000001</v>
+      </c>
+      <c r="D276" s="2">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>12</v>
+      </c>
+      <c r="B277">
+        <v>13187847</v>
+      </c>
+      <c r="C277">
+        <v>2287982.486</v>
+      </c>
+      <c r="D277" s="2">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>12</v>
+      </c>
+      <c r="B278">
+        <v>15988298</v>
+      </c>
+      <c r="C278">
+        <v>2631045.69</v>
+      </c>
+      <c r="D278" s="2">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>12</v>
+      </c>
+      <c r="B279">
+        <v>11489270</v>
+      </c>
+      <c r="C279">
+        <v>1890140.8049999999</v>
+      </c>
+      <c r="D279" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>12</v>
+      </c>
+      <c r="B280">
+        <v>12296935</v>
+      </c>
+      <c r="C280">
+        <v>2506551.1290000002</v>
+      </c>
+      <c r="D280" s="2">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281">
+        <v>21164992</v>
+      </c>
+      <c r="C281">
+        <v>3135596.9920000001</v>
+      </c>
+      <c r="D281" s="2">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>12</v>
+      </c>
+      <c r="B282">
+        <v>19880170</v>
+      </c>
+      <c r="C282">
+        <v>3619597.213</v>
+      </c>
+      <c r="D282" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>12</v>
+      </c>
+      <c r="B283">
+        <v>22076424</v>
+      </c>
+      <c r="C283">
+        <v>3341875.0210000002</v>
+      </c>
+      <c r="D283" s="2">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>12</v>
+      </c>
+      <c r="B284">
+        <v>12974512</v>
+      </c>
+      <c r="C284">
+        <v>2269817.281</v>
+      </c>
+      <c r="D284" s="2">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>12</v>
+      </c>
+      <c r="B285">
+        <v>15970061</v>
+      </c>
+      <c r="C285">
+        <v>2325150.17</v>
+      </c>
+      <c r="D285" s="2">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>12</v>
+      </c>
+      <c r="B286">
+        <v>9630956</v>
+      </c>
+      <c r="C286">
+        <v>1540122.875</v>
+      </c>
+      <c r="D286" s="2">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>12</v>
+      </c>
+      <c r="B287">
+        <v>12631821</v>
+      </c>
+      <c r="C287">
+        <v>2184328.7519999999</v>
+      </c>
+      <c r="D287" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>12</v>
+      </c>
+      <c r="B288">
+        <v>15028062</v>
+      </c>
+      <c r="C288">
+        <v>2687425.767</v>
+      </c>
+      <c r="D288" s="2">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>12</v>
+      </c>
+      <c r="B289">
+        <v>8461771</v>
+      </c>
+      <c r="C289">
+        <v>1390726.5589999999</v>
+      </c>
+      <c r="D289" s="2">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290">
+        <v>11360840</v>
+      </c>
+      <c r="C290">
+        <v>2065269.5</v>
+      </c>
+      <c r="D290" s="2">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>12</v>
+      </c>
+      <c r="B291">
+        <v>11025302</v>
+      </c>
+      <c r="C291">
+        <v>1651044.1880000001</v>
+      </c>
+      <c r="D291" s="2">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>12</v>
+      </c>
+      <c r="B292">
+        <v>13330221</v>
+      </c>
+      <c r="C292">
+        <v>1716202.781</v>
+      </c>
+      <c r="D292" s="2">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>12</v>
+      </c>
+      <c r="B293">
+        <v>19226916</v>
+      </c>
+      <c r="C293">
+        <v>3449547.0329999998</v>
+      </c>
+      <c r="D293" s="2">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>12</v>
+      </c>
+      <c r="B294">
+        <v>19810303</v>
+      </c>
+      <c r="C294">
+        <v>3518560.929</v>
+      </c>
+      <c r="D294" s="2">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>12</v>
+      </c>
+      <c r="B295">
+        <v>17508681</v>
+      </c>
+      <c r="C295">
+        <v>2721293.023</v>
+      </c>
+      <c r="D295" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>12</v>
+      </c>
+      <c r="B296">
+        <v>13518711</v>
+      </c>
+      <c r="C296">
+        <v>2463913.5460000001</v>
+      </c>
+      <c r="D296" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>12</v>
+      </c>
+      <c r="B297">
+        <v>12400854</v>
+      </c>
+      <c r="C297">
+        <v>2215963.9500000002</v>
+      </c>
+      <c r="D297" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>12</v>
+      </c>
+      <c r="B298">
+        <v>12741531</v>
+      </c>
+      <c r="C298">
+        <v>1898516.74</v>
+      </c>
+      <c r="D298" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299">
+        <v>16167842</v>
+      </c>
+      <c r="C299">
+        <v>2556914.17</v>
+      </c>
+      <c r="D299" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>12</v>
+      </c>
+      <c r="B300">
+        <v>15939959</v>
+      </c>
+      <c r="C300">
+        <v>2853586.7949999999</v>
+      </c>
+      <c r="D300" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>12</v>
+      </c>
+      <c r="B301">
+        <v>13192717</v>
+      </c>
+      <c r="C301">
+        <v>1959299.0009999999</v>
+      </c>
+      <c r="D301" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>12</v>
+      </c>
+      <c r="B302">
+        <v>13181146</v>
+      </c>
+      <c r="C302">
+        <v>3167550.7379999999</v>
+      </c>
+      <c r="D302" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>12</v>
+      </c>
+      <c r="B303">
+        <v>11028912</v>
+      </c>
+      <c r="C303">
+        <v>1554950.2109999999</v>
+      </c>
+      <c r="D303" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>12</v>
+      </c>
+      <c r="B304">
+        <v>12653087</v>
+      </c>
+      <c r="C304">
+        <v>2336888.3080000002</v>
+      </c>
+      <c r="D304" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>12</v>
+      </c>
+      <c r="B305">
+        <v>17190740</v>
+      </c>
+      <c r="C305">
+        <v>3255938.4010000001</v>
+      </c>
+      <c r="D305" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>12</v>
+      </c>
+      <c r="B306">
+        <v>18378061</v>
+      </c>
+      <c r="C306">
+        <v>3052461.165</v>
+      </c>
+      <c r="D306" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>12</v>
+      </c>
+      <c r="B307">
+        <v>19333957</v>
+      </c>
+      <c r="C307">
+        <v>2914391.594</v>
+      </c>
+      <c r="D307" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>12</v>
+      </c>
+      <c r="B308">
+        <v>13191999</v>
+      </c>
+      <c r="C308">
+        <v>2212291.4569999999</v>
+      </c>
+      <c r="D308" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>12</v>
+      </c>
+      <c r="B309">
+        <v>15876216</v>
+      </c>
+      <c r="C309">
+        <v>1858551.929</v>
+      </c>
+      <c r="D309" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>12</v>
+      </c>
+      <c r="B310">
+        <v>10004797</v>
+      </c>
+      <c r="C310">
+        <v>1536967.35</v>
+      </c>
+      <c r="D310" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>12</v>
+      </c>
+      <c r="B311">
+        <v>14537584</v>
+      </c>
+      <c r="C311">
+        <v>1934365.574</v>
+      </c>
+      <c r="D311" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>12</v>
+      </c>
+      <c r="B312">
+        <v>15581372</v>
+      </c>
+      <c r="C312">
+        <v>2360290.3709999998</v>
+      </c>
+      <c r="D312" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>12</v>
+      </c>
+      <c r="B313">
+        <v>12812040</v>
+      </c>
+      <c r="C313">
+        <v>2024295.3189999999</v>
+      </c>
+      <c r="D313" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>13</v>
+      </c>
+      <c r="B314">
+        <v>2119270</v>
+      </c>
+      <c r="C314">
+        <v>455983.19199999998</v>
+      </c>
+      <c r="D314" s="2">
+        <v>44562</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>13</v>
+      </c>
+      <c r="B315">
+        <v>3128795</v>
+      </c>
+      <c r="C315">
+        <v>616021.94200000004</v>
+      </c>
+      <c r="D315" s="2">
+        <v>44593</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>13</v>
+      </c>
+      <c r="B316">
+        <v>7010854</v>
+      </c>
+      <c r="C316">
+        <v>1204441.352</v>
+      </c>
+      <c r="D316" s="2">
+        <v>44621</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>13</v>
+      </c>
+      <c r="B317">
+        <v>4693321</v>
+      </c>
+      <c r="C317">
+        <v>1153746.8049999999</v>
+      </c>
+      <c r="D317" s="2">
+        <v>44652</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>13</v>
+      </c>
+      <c r="B318">
+        <v>4625707</v>
+      </c>
+      <c r="C318">
+        <v>627985.34499999997</v>
+      </c>
+      <c r="D318" s="2">
+        <v>44682</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>13</v>
+      </c>
+      <c r="B319">
+        <v>3184145</v>
+      </c>
+      <c r="C319">
+        <v>274518.44</v>
+      </c>
+      <c r="D319" s="2">
+        <v>44713</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>13</v>
+      </c>
+      <c r="B320">
+        <v>3114986</v>
+      </c>
+      <c r="C320">
+        <v>264239.53499999997</v>
+      </c>
+      <c r="D320" s="2">
+        <v>44743</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>13</v>
+      </c>
+      <c r="B321">
+        <v>2127995</v>
+      </c>
+      <c r="C321">
+        <v>158273.98000000001</v>
+      </c>
+      <c r="D321" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>13</v>
+      </c>
+      <c r="B322">
+        <v>413748</v>
+      </c>
+      <c r="C322">
+        <v>33114</v>
+      </c>
+      <c r="D322" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>13</v>
+      </c>
+      <c r="B323">
+        <v>340495</v>
+      </c>
+      <c r="C323">
+        <v>55834.5</v>
+      </c>
+      <c r="D323" s="2">
+        <v>44835</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>13</v>
+      </c>
+      <c r="B324">
+        <v>54684</v>
+      </c>
+      <c r="C324">
+        <v>4603.9799999999996</v>
+      </c>
+      <c r="D324" s="2">
+        <v>44866</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>13</v>
+      </c>
+      <c r="B325">
+        <v>484913</v>
+      </c>
+      <c r="C325">
+        <v>36607.199999999997</v>
+      </c>
+      <c r="D325" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>13</v>
+      </c>
+      <c r="B326">
+        <v>846912</v>
+      </c>
+      <c r="C326">
+        <v>45324.881000000001</v>
+      </c>
+      <c r="D326" s="2">
+        <v>44927</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>13</v>
+      </c>
+      <c r="B327">
+        <v>3823960</v>
+      </c>
+      <c r="C327">
+        <v>623765.58900000004</v>
+      </c>
+      <c r="D327" s="2">
+        <v>44958</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>13</v>
+      </c>
+      <c r="B328">
+        <v>3380891</v>
+      </c>
+      <c r="C328">
+        <v>343558.65</v>
+      </c>
+      <c r="D328" s="2">
+        <v>44986</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>13</v>
+      </c>
+      <c r="B329">
+        <v>3272085</v>
+      </c>
+      <c r="C329">
+        <v>327539.61599999998</v>
+      </c>
+      <c r="D329" s="2">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>13</v>
+      </c>
+      <c r="B330">
+        <v>3446965</v>
+      </c>
+      <c r="C330">
+        <v>302116.40999999997</v>
+      </c>
+      <c r="D330" s="2">
+        <v>45047</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>13</v>
+      </c>
+      <c r="B331">
+        <v>2698828</v>
+      </c>
+      <c r="C331">
+        <v>179619.19200000001</v>
+      </c>
+      <c r="D331" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>13</v>
+      </c>
+      <c r="B332">
+        <v>3141240</v>
+      </c>
+      <c r="C332">
+        <v>254473.83300000001</v>
+      </c>
+      <c r="D332" s="2">
+        <v>45108</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>13</v>
+      </c>
+      <c r="B333">
+        <v>2786014</v>
+      </c>
+      <c r="C333">
+        <v>197055.46</v>
+      </c>
+      <c r="D333" s="2">
+        <v>45139</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>13</v>
+      </c>
+      <c r="B334">
+        <v>380097</v>
+      </c>
+      <c r="C334">
+        <v>27168.678</v>
+      </c>
+      <c r="D334" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>13</v>
+      </c>
+      <c r="B335">
+        <v>38868</v>
+      </c>
+      <c r="C335">
+        <v>3628.88</v>
+      </c>
+      <c r="D335" s="2">
+        <v>45200</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>13</v>
+      </c>
+      <c r="B336">
+        <v>242452</v>
+      </c>
+      <c r="C336">
+        <v>18454.240000000002</v>
+      </c>
+      <c r="D336" s="2">
+        <v>45231</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>13</v>
+      </c>
+      <c r="B337">
+        <v>98064</v>
+      </c>
+      <c r="C337">
+        <v>5310.8</v>
+      </c>
+      <c r="D337" s="2">
+        <v>45261</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>13</v>
+      </c>
+      <c r="B338">
+        <v>977165</v>
+      </c>
+      <c r="C338">
+        <v>345976.11900000001</v>
+      </c>
+      <c r="D338" s="2">
+        <v>45292</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>13</v>
+      </c>
+      <c r="B339">
+        <v>3981243</v>
+      </c>
+      <c r="C339">
+        <v>1037549.347</v>
+      </c>
+      <c r="D339" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>13</v>
+      </c>
+      <c r="B340">
+        <v>3762253</v>
+      </c>
+      <c r="C340">
+        <v>732366.59</v>
+      </c>
+      <c r="D340" s="2">
+        <v>45352</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>13</v>
+      </c>
+      <c r="B341">
+        <v>2965261</v>
+      </c>
+      <c r="C341">
+        <v>291087.15999999997</v>
+      </c>
+      <c r="D341" s="2">
+        <v>45383</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>13</v>
+      </c>
+      <c r="B342">
+        <v>2171936</v>
+      </c>
+      <c r="C342">
+        <v>215121.45600000001</v>
+      </c>
+      <c r="D342" s="2">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>13</v>
+      </c>
+      <c r="B343">
+        <v>1330836</v>
+      </c>
+      <c r="C343">
+        <v>79372.740000000005</v>
+      </c>
+      <c r="D343" s="2">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>13</v>
+      </c>
+      <c r="B344">
+        <v>2771401</v>
+      </c>
+      <c r="C344">
+        <v>213271.64</v>
+      </c>
+      <c r="D344" s="2">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>13</v>
+      </c>
+      <c r="B345">
+        <v>1372034</v>
+      </c>
+      <c r="C345">
+        <v>109611.7</v>
+      </c>
+      <c r="D345" s="2">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>13</v>
+      </c>
+      <c r="B346">
+        <v>391197</v>
+      </c>
+      <c r="C346">
+        <v>24552.275000000001</v>
+      </c>
+      <c r="D346" s="2">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>13</v>
+      </c>
+      <c r="B347">
+        <v>62210</v>
+      </c>
+      <c r="C347">
+        <v>9257.65</v>
+      </c>
+      <c r="D347" s="2">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>13</v>
+      </c>
+      <c r="B348">
+        <v>51820</v>
+      </c>
+      <c r="C348">
+        <v>2792.8150000000001</v>
+      </c>
+      <c r="D348" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>13</v>
+      </c>
+      <c r="B349">
+        <v>297617</v>
+      </c>
+      <c r="C349">
+        <v>14362.791999999999</v>
+      </c>
+      <c r="D349" s="2">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>13</v>
+      </c>
+      <c r="B350">
+        <v>1550866</v>
+      </c>
+      <c r="C350">
+        <v>133920.39000000001</v>
+      </c>
+      <c r="D350" s="2">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>13</v>
+      </c>
+      <c r="B351">
+        <v>2297356</v>
+      </c>
+      <c r="C351">
+        <v>278539.68199999997</v>
+      </c>
+      <c r="D351" s="2">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>13</v>
+      </c>
+      <c r="B352">
+        <v>4602092</v>
+      </c>
+      <c r="C352">
+        <v>584659.48800000001</v>
+      </c>
+      <c r="D352" s="2">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>13</v>
+      </c>
+      <c r="B353">
+        <v>1595825</v>
+      </c>
+      <c r="C353">
+        <v>103037.74099999999</v>
+      </c>
+      <c r="D353" s="2">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>13</v>
+      </c>
+      <c r="B354">
+        <v>3774273</v>
+      </c>
+      <c r="C354">
+        <v>485333.66399999999</v>
+      </c>
+      <c r="D354" s="2">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>13</v>
+      </c>
+      <c r="B355">
+        <v>1155608</v>
+      </c>
+      <c r="C355">
+        <v>80377.25</v>
+      </c>
+      <c r="D355" s="2">
+        <v>45809</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>13</v>
+      </c>
+      <c r="B356">
+        <v>3036092</v>
+      </c>
+      <c r="C356">
+        <v>238192.89499999999</v>
+      </c>
+      <c r="D356" s="2">
+        <v>45839</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>13</v>
+      </c>
+      <c r="B357">
+        <v>1514470</v>
+      </c>
+      <c r="C357">
+        <v>115289.67600000001</v>
+      </c>
+      <c r="D357" s="2">
+        <v>45870</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>13</v>
+      </c>
+      <c r="B358">
+        <v>414617</v>
+      </c>
+      <c r="C358">
+        <v>31958</v>
+      </c>
+      <c r="D358" s="2">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>13</v>
+      </c>
+      <c r="B359">
+        <v>62423</v>
+      </c>
+      <c r="C359">
+        <v>26188.993999999999</v>
+      </c>
+      <c r="D359" s="2">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>13</v>
+      </c>
+      <c r="B360">
+        <v>158852</v>
+      </c>
+      <c r="C360">
+        <v>26073.61</v>
+      </c>
+      <c r="D360" s="2">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>13</v>
+      </c>
+      <c r="B361">
+        <v>120215</v>
+      </c>
+      <c r="C361">
+        <v>6405.04</v>
+      </c>
+      <c r="D361" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>13</v>
+      </c>
+      <c r="B362">
+        <v>162890</v>
+      </c>
+      <c r="C362">
+        <v>9709.6049999999996</v>
+      </c>
+      <c r="D362" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>13</v>
+      </c>
+      <c r="B363">
+        <v>1337568</v>
+      </c>
+      <c r="C363">
+        <v>187541.4</v>
+      </c>
+      <c r="D363" s="2">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>13</v>
+      </c>
+      <c r="B364">
+        <v>3403528</v>
+      </c>
+      <c r="C364">
+        <v>488674.13500000001</v>
+      </c>
+      <c r="D364" s="2">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>13</v>
+      </c>
+      <c r="B365">
+        <v>4229762</v>
+      </c>
+      <c r="C365">
+        <v>573086.76</v>
+      </c>
+      <c r="D365" s="2">
+        <v>46113</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/raw/manual_data.xlsx
+++ b/data/raw/manual_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mpinz-my.sharepoint.com/personal/federico_duranovich_mpi_govt_nz/Documents/Documents/Projects/R projects/autosopi/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fndur\Documents\Codex\2026-06-15\files-mentioned-by-the-user-theme\outputs\chart-framework\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_0A9A19B280FD5BAD86A44A52F313CA729B8CB82B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{370B21F5-9EAA-4046-9096-CF0FF8379437}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB610C8-E9D7-43FA-A04A-FD87957E36BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13560" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="kiwifruit_fig_1" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="18">
   <si>
     <t>category</t>
   </si>
@@ -851,7 +849,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C036DC8-EB82-436F-B554-7149B9FDDF6A}">
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -875,2451 +873,687 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>49210778</v>
+        <v>413842012</v>
       </c>
       <c r="D2">
-        <v>8956.3483980000001</v>
+        <v>35591.279560000003</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
       </c>
       <c r="C3">
-        <v>138920255</v>
+        <v>642572741</v>
       </c>
       <c r="D3">
-        <v>44188.423016999994</v>
+        <v>149883.6629917</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="C4">
-        <v>1544810</v>
+        <v>2779753</v>
       </c>
       <c r="D4">
-        <v>193.47049999999999</v>
+        <v>249.02866</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
       </c>
       <c r="C5">
-        <v>29761595</v>
+        <v>94578346</v>
       </c>
       <c r="D5">
-        <v>5376.589876</v>
+        <v>12531.365387</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6">
-        <v>34483827</v>
+        <v>389744481</v>
       </c>
       <c r="D6">
-        <v>857.02594799999997</v>
+        <v>5013.2682779999996</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>24497913</v>
+        <v>160141593</v>
       </c>
       <c r="D7">
-        <v>9950.5959340000009</v>
+        <v>29400.928701000001</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>2003</v>
+        <v>2021</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8">
-        <v>11021451</v>
+        <v>41080200</v>
       </c>
       <c r="D8">
-        <v>4966.5046359999997</v>
+        <v>9191.1073310000011</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9">
-        <v>178943441</v>
+        <v>475407664</v>
       </c>
       <c r="D9">
-        <v>34555.573042000004</v>
+        <v>42210.152661</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
       </c>
       <c r="C10">
-        <v>606808356</v>
+        <v>709170126</v>
       </c>
       <c r="D10">
-        <v>196663.59945199999</v>
+        <v>153859.90807</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11">
-        <v>6222912</v>
+        <v>3298420</v>
       </c>
       <c r="D11">
-        <v>670.91124000000002</v>
+        <v>256.070899</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
       </c>
       <c r="C12">
-        <v>100444646</v>
+        <v>95101446</v>
       </c>
       <c r="D12">
-        <v>18870.264496</v>
+        <v>13155.78377</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13">
-        <v>168725903</v>
+        <v>417005576</v>
       </c>
       <c r="D13">
-        <v>4213.259943</v>
+        <v>5513.862916</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14">
-        <v>111793276</v>
+        <v>160669575</v>
       </c>
       <c r="D14">
-        <v>49236.930121999998</v>
+        <v>32515.334282</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15">
-        <v>32267270</v>
+        <v>28948367</v>
       </c>
       <c r="D15">
-        <v>10622.737293</v>
+        <v>5448.1363940000001</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
       </c>
       <c r="C16">
-        <v>199314457</v>
+        <v>485426486</v>
       </c>
       <c r="D16">
-        <v>37630.911012000004</v>
+        <v>34652.7341916</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17">
-        <v>651229553</v>
+        <v>759108743</v>
       </c>
       <c r="D17">
-        <v>205533.763377</v>
+        <v>151259.950668</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
       <c r="C18">
-        <v>5129797</v>
+        <v>3017556</v>
       </c>
       <c r="D18">
-        <v>648.72895999999992</v>
+        <v>202.92854</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19">
-        <v>103144221</v>
+        <v>106927651</v>
       </c>
       <c r="D19">
-        <v>20704.034885000001</v>
+        <v>12601.5544711</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
       <c r="C20">
-        <v>170435660</v>
+        <v>443062248</v>
       </c>
       <c r="D20">
-        <v>4265.186573</v>
+        <v>4679.993802</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
       </c>
       <c r="C21">
-        <v>111385671</v>
+        <v>170747951</v>
       </c>
       <c r="D21">
-        <v>48497.701578</v>
+        <v>30085.331211000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
       </c>
       <c r="C22">
-        <v>33759102</v>
+        <v>27091757</v>
       </c>
       <c r="D22">
-        <v>14704.39465</v>
+        <v>3621.572905</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23">
-        <v>211717743</v>
+        <v>565177696</v>
       </c>
       <c r="D23">
-        <v>39344.716140000004</v>
+        <v>36142.823409999997</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="B24" t="s">
         <v>8</v>
       </c>
       <c r="C24">
-        <v>650526211</v>
+        <v>748339470</v>
       </c>
       <c r="D24">
-        <v>222486.63195399998</v>
+        <v>150971.77320899998</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
       </c>
       <c r="C25">
-        <v>5250158</v>
+        <v>4077829</v>
       </c>
       <c r="D25">
-        <v>604.92527199999995</v>
+        <v>424.93413699999996</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
       </c>
       <c r="C26">
-        <v>107056735</v>
+        <v>101009167</v>
       </c>
       <c r="D26">
-        <v>22217.814717999998</v>
+        <v>11364.318244999999</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
       </c>
       <c r="C27">
-        <v>168513396</v>
+        <v>535880233</v>
       </c>
       <c r="D27">
-        <v>4441.0747670000001</v>
+        <v>5058.7055399999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="s">
         <v>12</v>
       </c>
       <c r="C28">
-        <v>99105333</v>
+        <v>182319348</v>
       </c>
       <c r="D28">
-        <v>42531.924664999999</v>
+        <v>30419.634181000001</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>2006</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
       <c r="C29">
-        <v>28942548</v>
+        <v>24825274</v>
       </c>
       <c r="D29">
-        <v>13653.50232</v>
+        <v>3431.2591649999999</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
       </c>
       <c r="C30">
-        <v>249292467</v>
+        <v>643817340</v>
       </c>
       <c r="D30">
-        <v>43833.867634999995</v>
+        <v>37691.231806000003</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
       </c>
       <c r="C31">
-        <v>596321521</v>
+        <v>821108855</v>
       </c>
       <c r="D31">
-        <v>185776.82144100001</v>
+        <v>150584.723157</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
       </c>
       <c r="C32">
-        <v>6337876</v>
+        <v>4647813</v>
       </c>
       <c r="D32">
-        <v>685.00874699999997</v>
+        <v>319.72566399999999</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
       </c>
       <c r="C33">
-        <v>116354988</v>
+        <v>106383073</v>
       </c>
       <c r="D33">
-        <v>20659.344965</v>
+        <v>11044.424333000001</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
       </c>
       <c r="C34">
-        <v>217453649</v>
+        <v>435323044</v>
       </c>
       <c r="D34">
-        <v>5270.4025700000002</v>
+        <v>4797.1812010000003</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
       </c>
       <c r="C35">
-        <v>137106217</v>
+        <v>171492931</v>
       </c>
       <c r="D35">
-        <v>47412.595538000001</v>
+        <v>28501.539214</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>2007</v>
+        <v>2025</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36">
-        <v>29974323</v>
+        <v>19864626</v>
       </c>
       <c r="D36">
-        <v>13225.926670000001</v>
+        <v>1956.549788</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="B37" t="s">
         <v>7</v>
       </c>
       <c r="C37">
-        <v>217545289</v>
+        <v>596151630</v>
       </c>
       <c r="D37">
-        <v>39376.649764000002</v>
+        <v>36183.326389000002</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="B38" t="s">
         <v>8</v>
       </c>
       <c r="C38">
-        <v>544383886</v>
+        <v>935058835</v>
       </c>
       <c r="D38">
-        <v>201940.92255700001</v>
+        <v>153360.59449399999</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
       </c>
       <c r="C39">
-        <v>6441754</v>
+        <v>5716105</v>
       </c>
       <c r="D39">
-        <v>871.40002800000002</v>
+        <v>407.22276899999997</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="B40" t="s">
         <v>10</v>
       </c>
       <c r="C40">
-        <v>110087383</v>
+        <v>121478600</v>
       </c>
       <c r="D40">
-        <v>17701.035486000001</v>
+        <v>13202.070623</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="B41" t="s">
         <v>11</v>
       </c>
       <c r="C41">
-        <v>204030000</v>
+        <v>335893048</v>
       </c>
       <c r="D41">
-        <v>4929.437602</v>
+        <v>4103.2785709999998</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="B42" t="s">
         <v>12</v>
       </c>
       <c r="C42">
-        <v>118627925</v>
+        <v>174150588</v>
       </c>
       <c r="D42">
-        <v>39949.405663000005</v>
+        <v>28143.946099000001</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
       </c>
       <c r="C43">
-        <v>43304041</v>
+        <v>16736361</v>
       </c>
       <c r="D43">
-        <v>16568.539980000001</v>
+        <v>1798.7820099999999</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>2009</v>
+        <v>2027</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
       </c>
       <c r="C44">
-        <v>295649805</v>
+        <v>51043704</v>
       </c>
       <c r="D44">
-        <v>38856.126413000005</v>
+        <v>3248.7946830000001</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>2009</v>
+        <v>2027</v>
       </c>
       <c r="B45" t="s">
         <v>8</v>
       </c>
       <c r="C45">
-        <v>582560960</v>
+        <v>100140559</v>
       </c>
       <c r="D45">
-        <v>173979.85563400001</v>
+        <v>12906.282364000001</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>2009</v>
+        <v>2027</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
       </c>
       <c r="C46">
-        <v>5074706</v>
+        <v>468895</v>
       </c>
       <c r="D46">
-        <v>526.77554799999996</v>
+        <v>26.192430999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>2009</v>
+        <v>2027</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
       </c>
       <c r="C47">
-        <v>121127469</v>
+        <v>10624007</v>
       </c>
       <c r="D47">
-        <v>16750.837909999998</v>
+        <v>1278.9460220000001</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>2009</v>
+        <v>2027</v>
       </c>
       <c r="B48" t="s">
         <v>11</v>
       </c>
       <c r="C48">
-        <v>248322304</v>
+        <v>36653386</v>
       </c>
       <c r="D48">
-        <v>4453.6324289999993</v>
+        <v>315.75279999999998</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>2009</v>
+        <v>2027</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
       </c>
       <c r="C49">
-        <v>152038226</v>
+        <v>12812040</v>
       </c>
       <c r="D49">
-        <v>41038.180781000003</v>
+        <v>2024.2953189999998</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>2009</v>
+        <v>2027</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
       </c>
       <c r="C50">
-        <v>33420331</v>
+        <v>4229762</v>
       </c>
       <c r="D50">
-        <v>9514.4331999999995</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>2010</v>
-      </c>
-      <c r="B51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51">
-        <v>255639841</v>
-      </c>
-      <c r="D51">
-        <v>41176.750226999997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>2010</v>
-      </c>
-      <c r="B52" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52">
-        <v>549712116</v>
-      </c>
-      <c r="D52">
-        <v>176533.93288800001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>2010</v>
-      </c>
-      <c r="B53" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53">
-        <v>5819632</v>
-      </c>
-      <c r="D53">
-        <v>985.73194999999998</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>2010</v>
-      </c>
-      <c r="B54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54">
-        <v>118550800</v>
-      </c>
-      <c r="D54">
-        <v>17098.849554</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>2010</v>
-      </c>
-      <c r="B55" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55">
-        <v>245851020</v>
-      </c>
-      <c r="D55">
-        <v>4629.2716879999998</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>2010</v>
-      </c>
-      <c r="B56" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56">
-        <v>166281516</v>
-      </c>
-      <c r="D56">
-        <v>42192.127447999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>2010</v>
-      </c>
-      <c r="B57" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57">
-        <v>33525549</v>
-      </c>
-      <c r="D57">
-        <v>8659.7714700000015</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>2011</v>
-      </c>
-      <c r="B58" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58">
-        <v>286829645</v>
-      </c>
-      <c r="D58">
-        <v>44001.363031000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>2011</v>
-      </c>
-      <c r="B59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59">
-        <v>605347183</v>
-      </c>
-      <c r="D59">
-        <v>180318.69835699999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>2011</v>
-      </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60">
-        <v>6541424</v>
-      </c>
-      <c r="D60">
-        <v>1404.82927</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>2011</v>
-      </c>
-      <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61">
-        <v>124865510</v>
-      </c>
-      <c r="D61">
-        <v>19686.394397999997</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>2011</v>
-      </c>
-      <c r="B62" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62">
-        <v>289604021</v>
-      </c>
-      <c r="D62">
-        <v>4904.9726109999992</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>2011</v>
-      </c>
-      <c r="B63" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63">
-        <v>161558816</v>
-      </c>
-      <c r="D63">
-        <v>41377.092611</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>2011</v>
-      </c>
-      <c r="B64" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64">
-        <v>53980294</v>
-      </c>
-      <c r="D64">
-        <v>17536.286478000002</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>2012</v>
-      </c>
-      <c r="B65" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65">
-        <v>306724696</v>
-      </c>
-      <c r="D65">
-        <v>44755.962056000004</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>2012</v>
-      </c>
-      <c r="B66" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66">
-        <v>621004577</v>
-      </c>
-      <c r="D66">
-        <v>179503.60314700002</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>2012</v>
-      </c>
-      <c r="B67" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67">
-        <v>8531671</v>
-      </c>
-      <c r="D67">
-        <v>763.35318000000007</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>2012</v>
-      </c>
-      <c r="B68" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68">
-        <v>123163363</v>
-      </c>
-      <c r="D68">
-        <v>18742.676194</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>2012</v>
-      </c>
-      <c r="B69" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69">
-        <v>292625096.69999999</v>
-      </c>
-      <c r="D69">
-        <v>4775.8031380000002</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>2012</v>
-      </c>
-      <c r="B70" t="s">
-        <v>12</v>
-      </c>
-      <c r="C70">
-        <v>147267770</v>
-      </c>
-      <c r="D70">
-        <v>38801.498607000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>2012</v>
-      </c>
-      <c r="B71" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71">
-        <v>63114307</v>
-      </c>
-      <c r="D71">
-        <v>17952.709125999998</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>2013</v>
-      </c>
-      <c r="B72" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72">
-        <v>279671036</v>
-      </c>
-      <c r="D72">
-        <v>39720.057249999998</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>2013</v>
-      </c>
-      <c r="B73" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73">
-        <v>621495623</v>
-      </c>
-      <c r="D73">
-        <v>184090.33204899999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>2013</v>
-      </c>
-      <c r="B74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74">
-        <v>8831881</v>
-      </c>
-      <c r="D74">
-        <v>716.58881000000008</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>2013</v>
-      </c>
-      <c r="B75" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75">
-        <v>124029387</v>
-      </c>
-      <c r="D75">
-        <v>18198.857623</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>2013</v>
-      </c>
-      <c r="B76" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76">
-        <v>287877836</v>
-      </c>
-      <c r="D76">
-        <v>4849.2356469999995</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>2013</v>
-      </c>
-      <c r="B77" t="s">
-        <v>12</v>
-      </c>
-      <c r="C77">
-        <v>178600643</v>
-      </c>
-      <c r="D77">
-        <v>40899.634092</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>2013</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78">
-        <v>73583368</v>
-      </c>
-      <c r="D78">
-        <v>17248.986024999998</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>2014</v>
-      </c>
-      <c r="B79" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79">
-        <v>307818253</v>
-      </c>
-      <c r="D79">
-        <v>36000.370699999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>2014</v>
-      </c>
-      <c r="B80" t="s">
-        <v>8</v>
-      </c>
-      <c r="C80">
-        <v>564604255</v>
-      </c>
-      <c r="D80">
-        <v>167634.540614</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>2014</v>
-      </c>
-      <c r="B81" t="s">
-        <v>9</v>
-      </c>
-      <c r="C81">
-        <v>8690974</v>
-      </c>
-      <c r="D81">
-        <v>697.040525</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>2014</v>
-      </c>
-      <c r="B82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82">
-        <v>110755129</v>
-      </c>
-      <c r="D82">
-        <v>18344.484243999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>2014</v>
-      </c>
-      <c r="B83" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83">
-        <v>311602272</v>
-      </c>
-      <c r="D83">
-        <v>4884.6634649999996</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>2014</v>
-      </c>
-      <c r="B84" t="s">
-        <v>12</v>
-      </c>
-      <c r="C84">
-        <v>157512967</v>
-      </c>
-      <c r="D84">
-        <v>42734.877699000004</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>2014</v>
-      </c>
-      <c r="B85" t="s">
-        <v>13</v>
-      </c>
-      <c r="C85">
-        <v>55038775</v>
-      </c>
-      <c r="D85">
-        <v>15749.834237999999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>2015</v>
-      </c>
-      <c r="B86" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86">
-        <v>322798057</v>
-      </c>
-      <c r="D86">
-        <v>34824.978967000003</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>2015</v>
-      </c>
-      <c r="B87" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87">
-        <v>571423766</v>
-      </c>
-      <c r="D87">
-        <v>176192.453916</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>2015</v>
-      </c>
-      <c r="B88" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88">
-        <v>6203391</v>
-      </c>
-      <c r="D88">
-        <v>542.46620999999993</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>2015</v>
-      </c>
-      <c r="B89" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89">
-        <v>106437183</v>
-      </c>
-      <c r="D89">
-        <v>17192.579462999998</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>2015</v>
-      </c>
-      <c r="B90" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90">
-        <v>329352469</v>
-      </c>
-      <c r="D90">
-        <v>4823.4095980000002</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>2015</v>
-      </c>
-      <c r="B91" t="s">
-        <v>12</v>
-      </c>
-      <c r="C91">
-        <v>142691385</v>
-      </c>
-      <c r="D91">
-        <v>39427.274676000001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>2015</v>
-      </c>
-      <c r="B92" t="s">
-        <v>13</v>
-      </c>
-      <c r="C92">
-        <v>54520056</v>
-      </c>
-      <c r="D92">
-        <v>23243.808736000003</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93">
-        <v>2016</v>
-      </c>
-      <c r="B93" t="s">
-        <v>7</v>
-      </c>
-      <c r="C93">
-        <v>364722214</v>
-      </c>
-      <c r="D93">
-        <v>34872.460674000002</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>2016</v>
-      </c>
-      <c r="B94" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94">
-        <v>651207039.95000005</v>
-      </c>
-      <c r="D94">
-        <v>182538.898736</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>2016</v>
-      </c>
-      <c r="B95" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95">
-        <v>5279696</v>
-      </c>
-      <c r="D95">
-        <v>467.57496999999995</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96">
-        <v>2016</v>
-      </c>
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96">
-        <v>105620592</v>
-      </c>
-      <c r="D96">
-        <v>15575.154119999999</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97">
-        <v>2016</v>
-      </c>
-      <c r="B97" t="s">
-        <v>11</v>
-      </c>
-      <c r="C97">
-        <v>377045402</v>
-      </c>
-      <c r="D97">
-        <v>5134.9797369999997</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>2016</v>
-      </c>
-      <c r="B98" t="s">
-        <v>12</v>
-      </c>
-      <c r="C98">
-        <v>156201734</v>
-      </c>
-      <c r="D98">
-        <v>38595.699746999999</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>2016</v>
-      </c>
-      <c r="B99" t="s">
-        <v>13</v>
-      </c>
-      <c r="C99">
-        <v>48365573</v>
-      </c>
-      <c r="D99">
-        <v>14100.390739</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100">
-        <v>2017</v>
-      </c>
-      <c r="B100" t="s">
-        <v>7</v>
-      </c>
-      <c r="C100">
-        <v>396741679</v>
-      </c>
-      <c r="D100">
-        <v>39063.285178999999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>2017</v>
-      </c>
-      <c r="B101" t="s">
-        <v>8</v>
-      </c>
-      <c r="C101">
-        <v>678527769</v>
-      </c>
-      <c r="D101">
-        <v>181357.966717</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102">
-        <v>2017</v>
-      </c>
-      <c r="B102" t="s">
-        <v>9</v>
-      </c>
-      <c r="C102">
-        <v>4574206</v>
-      </c>
-      <c r="D102">
-        <v>467.02042</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103">
-        <v>2017</v>
-      </c>
-      <c r="B103" t="s">
-        <v>10</v>
-      </c>
-      <c r="C103">
-        <v>107200083</v>
-      </c>
-      <c r="D103">
-        <v>15862.751808000001</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104">
-        <v>2017</v>
-      </c>
-      <c r="B104" t="s">
-        <v>11</v>
-      </c>
-      <c r="C104">
-        <v>360775068</v>
-      </c>
-      <c r="D104">
-        <v>5024.4978519999995</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A105">
-        <v>2017</v>
-      </c>
-      <c r="B105" t="s">
-        <v>12</v>
-      </c>
-      <c r="C105">
-        <v>151058518</v>
-      </c>
-      <c r="D105">
-        <v>37520.171964000001</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A106">
-        <v>2017</v>
-      </c>
-      <c r="B106" t="s">
-        <v>13</v>
-      </c>
-      <c r="C106">
-        <v>48072984</v>
-      </c>
-      <c r="D106">
-        <v>10902.275152</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A107">
-        <v>2018</v>
-      </c>
-      <c r="B107" t="s">
-        <v>7</v>
-      </c>
-      <c r="C107">
-        <v>424775369</v>
-      </c>
-      <c r="D107">
-        <v>42027.147203</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A108">
-        <v>2018</v>
-      </c>
-      <c r="B108" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108">
-        <v>726600728</v>
-      </c>
-      <c r="D108">
-        <v>177825.68732499998</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A109">
-        <v>2018</v>
-      </c>
-      <c r="B109" t="s">
-        <v>9</v>
-      </c>
-      <c r="C109">
-        <v>5490467</v>
-      </c>
-      <c r="D109">
-        <v>530.33391200000005</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A110">
-        <v>2018</v>
-      </c>
-      <c r="B110" t="s">
-        <v>10</v>
-      </c>
-      <c r="C110">
-        <v>110099392</v>
-      </c>
-      <c r="D110">
-        <v>16110.762795000001</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A111">
-        <v>2018</v>
-      </c>
-      <c r="B111" t="s">
-        <v>11</v>
-      </c>
-      <c r="C111">
-        <v>334852277</v>
-      </c>
-      <c r="D111">
-        <v>5043.422802</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A112">
-        <v>2018</v>
-      </c>
-      <c r="B112" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112">
-        <v>151911137</v>
-      </c>
-      <c r="D112">
-        <v>38341.803159999996</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A113">
-        <v>2018</v>
-      </c>
-      <c r="B113" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113">
-        <v>39092461</v>
-      </c>
-      <c r="D113">
-        <v>8637.1327070000007</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A114">
-        <v>2019</v>
-      </c>
-      <c r="B114" t="s">
-        <v>7</v>
-      </c>
-      <c r="C114">
-        <v>433899463</v>
-      </c>
-      <c r="D114">
-        <v>38215.240299000005</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A115">
-        <v>2019</v>
-      </c>
-      <c r="B115" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115">
-        <v>735521372</v>
-      </c>
-      <c r="D115">
-        <v>167008.03877499999</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A116">
-        <v>2019</v>
-      </c>
-      <c r="B116" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116">
-        <v>4680996</v>
-      </c>
-      <c r="D116">
-        <v>439.26035999999999</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>2019</v>
-      </c>
-      <c r="B117" t="s">
-        <v>10</v>
-      </c>
-      <c r="C117">
-        <v>101834961</v>
-      </c>
-      <c r="D117">
-        <v>14253.087669</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>2019</v>
-      </c>
-      <c r="B118" t="s">
-        <v>11</v>
-      </c>
-      <c r="C118">
-        <v>388684690</v>
-      </c>
-      <c r="D118">
-        <v>5133.0389529999993</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A119">
-        <v>2019</v>
-      </c>
-      <c r="B119" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119">
-        <v>158522573</v>
-      </c>
-      <c r="D119">
-        <v>37479.806023000005</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A120">
-        <v>2019</v>
-      </c>
-      <c r="B120" t="s">
-        <v>13</v>
-      </c>
-      <c r="C120">
-        <v>45201522</v>
-      </c>
-      <c r="D120">
-        <v>9581.9871400000011</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A121">
-        <v>2020</v>
-      </c>
-      <c r="B121" t="s">
-        <v>7</v>
-      </c>
-      <c r="C121">
-        <v>483108135</v>
-      </c>
-      <c r="D121">
-        <v>39225.543194999998</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A122">
-        <v>2020</v>
-      </c>
-      <c r="B122" t="s">
-        <v>8</v>
-      </c>
-      <c r="C122">
-        <v>855370821</v>
-      </c>
-      <c r="D122">
-        <v>177967.59181000001</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A123">
-        <v>2020</v>
-      </c>
-      <c r="B123" t="s">
-        <v>9</v>
-      </c>
-      <c r="C123">
-        <v>3928321</v>
-      </c>
-      <c r="D123">
-        <v>331.13237300000003</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A124">
-        <v>2020</v>
-      </c>
-      <c r="B124" t="s">
-        <v>10</v>
-      </c>
-      <c r="C124">
-        <v>97786745</v>
-      </c>
-      <c r="D124">
-        <v>12948.267211999999</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A125">
-        <v>2020</v>
-      </c>
-      <c r="B125" t="s">
-        <v>11</v>
-      </c>
-      <c r="C125">
-        <v>327405154</v>
-      </c>
-      <c r="D125">
-        <v>4742.0749529999994</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A126">
-        <v>2020</v>
-      </c>
-      <c r="B126" t="s">
-        <v>12</v>
-      </c>
-      <c r="C126">
-        <v>165748833</v>
-      </c>
-      <c r="D126">
-        <v>35575.104102999998</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A127">
-        <v>2020</v>
-      </c>
-      <c r="B127" t="s">
-        <v>13</v>
-      </c>
-      <c r="C127">
-        <v>56302272</v>
-      </c>
-      <c r="D127">
-        <v>11882.785937999999</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A128">
-        <v>2021</v>
-      </c>
-      <c r="B128" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128">
-        <v>413842012</v>
-      </c>
-      <c r="D128">
-        <v>35591.279560000003</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A129">
-        <v>2021</v>
-      </c>
-      <c r="B129" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129">
-        <v>642572741</v>
-      </c>
-      <c r="D129">
-        <v>149883.6629917</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A130">
-        <v>2021</v>
-      </c>
-      <c r="B130" t="s">
-        <v>9</v>
-      </c>
-      <c r="C130">
-        <v>2779753</v>
-      </c>
-      <c r="D130">
-        <v>249.02866</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A131">
-        <v>2021</v>
-      </c>
-      <c r="B131" t="s">
-        <v>10</v>
-      </c>
-      <c r="C131">
-        <v>94578346</v>
-      </c>
-      <c r="D131">
-        <v>12531.365387</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A132">
-        <v>2021</v>
-      </c>
-      <c r="B132" t="s">
-        <v>11</v>
-      </c>
-      <c r="C132">
-        <v>389744481</v>
-      </c>
-      <c r="D132">
-        <v>5013.2682779999996</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A133">
-        <v>2021</v>
-      </c>
-      <c r="B133" t="s">
-        <v>12</v>
-      </c>
-      <c r="C133">
-        <v>160141593</v>
-      </c>
-      <c r="D133">
-        <v>29400.928701000001</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A134">
-        <v>2021</v>
-      </c>
-      <c r="B134" t="s">
-        <v>13</v>
-      </c>
-      <c r="C134">
-        <v>41080200</v>
-      </c>
-      <c r="D134">
-        <v>9191.1073310000011</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A135">
-        <v>2022</v>
-      </c>
-      <c r="B135" t="s">
-        <v>7</v>
-      </c>
-      <c r="C135">
-        <v>475407664</v>
-      </c>
-      <c r="D135">
-        <v>42210.152661</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A136">
-        <v>2022</v>
-      </c>
-      <c r="B136" t="s">
-        <v>8</v>
-      </c>
-      <c r="C136">
-        <v>709170126</v>
-      </c>
-      <c r="D136">
-        <v>153859.90807</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A137">
-        <v>2022</v>
-      </c>
-      <c r="B137" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137">
-        <v>3298420</v>
-      </c>
-      <c r="D137">
-        <v>256.070899</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A138">
-        <v>2022</v>
-      </c>
-      <c r="B138" t="s">
-        <v>10</v>
-      </c>
-      <c r="C138">
-        <v>95101446</v>
-      </c>
-      <c r="D138">
-        <v>13155.78377</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A139">
-        <v>2022</v>
-      </c>
-      <c r="B139" t="s">
-        <v>11</v>
-      </c>
-      <c r="C139">
-        <v>417005576</v>
-      </c>
-      <c r="D139">
-        <v>5513.862916</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A140">
-        <v>2022</v>
-      </c>
-      <c r="B140" t="s">
-        <v>12</v>
-      </c>
-      <c r="C140">
-        <v>160669575</v>
-      </c>
-      <c r="D140">
-        <v>32515.334282</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A141">
-        <v>2022</v>
-      </c>
-      <c r="B141" t="s">
-        <v>13</v>
-      </c>
-      <c r="C141">
-        <v>28948367</v>
-      </c>
-      <c r="D141">
-        <v>5448.1363940000001</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A142">
-        <v>2023</v>
-      </c>
-      <c r="B142" t="s">
-        <v>7</v>
-      </c>
-      <c r="C142">
-        <v>485426486</v>
-      </c>
-      <c r="D142">
-        <v>34652.7341916</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A143">
-        <v>2023</v>
-      </c>
-      <c r="B143" t="s">
-        <v>8</v>
-      </c>
-      <c r="C143">
-        <v>759108743</v>
-      </c>
-      <c r="D143">
-        <v>151259.950668</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A144">
-        <v>2023</v>
-      </c>
-      <c r="B144" t="s">
-        <v>9</v>
-      </c>
-      <c r="C144">
-        <v>3017556</v>
-      </c>
-      <c r="D144">
-        <v>202.92854</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145">
-        <v>2023</v>
-      </c>
-      <c r="B145" t="s">
-        <v>10</v>
-      </c>
-      <c r="C145">
-        <v>106927651</v>
-      </c>
-      <c r="D145">
-        <v>12601.5544711</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146">
-        <v>2023</v>
-      </c>
-      <c r="B146" t="s">
-        <v>11</v>
-      </c>
-      <c r="C146">
-        <v>443062248</v>
-      </c>
-      <c r="D146">
-        <v>4679.993802</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147">
-        <v>2023</v>
-      </c>
-      <c r="B147" t="s">
-        <v>12</v>
-      </c>
-      <c r="C147">
-        <v>170747951</v>
-      </c>
-      <c r="D147">
-        <v>30085.331211000001</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A148">
-        <v>2023</v>
-      </c>
-      <c r="B148" t="s">
-        <v>13</v>
-      </c>
-      <c r="C148">
-        <v>27091757</v>
-      </c>
-      <c r="D148">
-        <v>3621.572905</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149">
-        <v>2024</v>
-      </c>
-      <c r="B149" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149">
-        <v>565177696</v>
-      </c>
-      <c r="D149">
-        <v>36142.823409999997</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150">
-        <v>2024</v>
-      </c>
-      <c r="B150" t="s">
-        <v>8</v>
-      </c>
-      <c r="C150">
-        <v>748339470</v>
-      </c>
-      <c r="D150">
-        <v>150971.77320899998</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151">
-        <v>2024</v>
-      </c>
-      <c r="B151" t="s">
-        <v>9</v>
-      </c>
-      <c r="C151">
-        <v>4077829</v>
-      </c>
-      <c r="D151">
-        <v>424.93413699999996</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152">
-        <v>2024</v>
-      </c>
-      <c r="B152" t="s">
-        <v>10</v>
-      </c>
-      <c r="C152">
-        <v>101009167</v>
-      </c>
-      <c r="D152">
-        <v>11364.318244999999</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A153">
-        <v>2024</v>
-      </c>
-      <c r="B153" t="s">
-        <v>11</v>
-      </c>
-      <c r="C153">
-        <v>535880233</v>
-      </c>
-      <c r="D153">
-        <v>5058.7055399999999</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A154">
-        <v>2024</v>
-      </c>
-      <c r="B154" t="s">
-        <v>12</v>
-      </c>
-      <c r="C154">
-        <v>182319348</v>
-      </c>
-      <c r="D154">
-        <v>30419.634181000001</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A155">
-        <v>2024</v>
-      </c>
-      <c r="B155" t="s">
-        <v>13</v>
-      </c>
-      <c r="C155">
-        <v>24825274</v>
-      </c>
-      <c r="D155">
-        <v>3431.2591649999999</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A156">
-        <v>2025</v>
-      </c>
-      <c r="B156" t="s">
-        <v>7</v>
-      </c>
-      <c r="C156">
-        <v>643817340</v>
-      </c>
-      <c r="D156">
-        <v>37691.231806000003</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A157">
-        <v>2025</v>
-      </c>
-      <c r="B157" t="s">
-        <v>8</v>
-      </c>
-      <c r="C157">
-        <v>821108855</v>
-      </c>
-      <c r="D157">
-        <v>150584.723157</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A158">
-        <v>2025</v>
-      </c>
-      <c r="B158" t="s">
-        <v>9</v>
-      </c>
-      <c r="C158">
-        <v>4647813</v>
-      </c>
-      <c r="D158">
-        <v>319.72566399999999</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A159">
-        <v>2025</v>
-      </c>
-      <c r="B159" t="s">
-        <v>10</v>
-      </c>
-      <c r="C159">
-        <v>106383073</v>
-      </c>
-      <c r="D159">
-        <v>11044.424333000001</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A160">
-        <v>2025</v>
-      </c>
-      <c r="B160" t="s">
-        <v>11</v>
-      </c>
-      <c r="C160">
-        <v>435323044</v>
-      </c>
-      <c r="D160">
-        <v>4797.1812010000003</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A161">
-        <v>2025</v>
-      </c>
-      <c r="B161" t="s">
-        <v>12</v>
-      </c>
-      <c r="C161">
-        <v>171492931</v>
-      </c>
-      <c r="D161">
-        <v>28501.539214</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A162">
-        <v>2025</v>
-      </c>
-      <c r="B162" t="s">
-        <v>13</v>
-      </c>
-      <c r="C162">
-        <v>19864626</v>
-      </c>
-      <c r="D162">
-        <v>1956.549788</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A163">
-        <v>2026</v>
-      </c>
-      <c r="B163" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163">
-        <v>596151630</v>
-      </c>
-      <c r="D163">
-        <v>36183.326389000002</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A164">
-        <v>2026</v>
-      </c>
-      <c r="B164" t="s">
-        <v>8</v>
-      </c>
-      <c r="C164">
-        <v>935058835</v>
-      </c>
-      <c r="D164">
-        <v>153360.59449399999</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A165">
-        <v>2026</v>
-      </c>
-      <c r="B165" t="s">
-        <v>9</v>
-      </c>
-      <c r="C165">
-        <v>5716105</v>
-      </c>
-      <c r="D165">
-        <v>407.22276899999997</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A166">
-        <v>2026</v>
-      </c>
-      <c r="B166" t="s">
-        <v>10</v>
-      </c>
-      <c r="C166">
-        <v>121478600</v>
-      </c>
-      <c r="D166">
-        <v>13202.070623</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A167">
-        <v>2026</v>
-      </c>
-      <c r="B167" t="s">
-        <v>11</v>
-      </c>
-      <c r="C167">
-        <v>335893048</v>
-      </c>
-      <c r="D167">
-        <v>4103.2785709999998</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A168">
-        <v>2026</v>
-      </c>
-      <c r="B168" t="s">
-        <v>12</v>
-      </c>
-      <c r="C168">
-        <v>174150588</v>
-      </c>
-      <c r="D168">
-        <v>28143.946099000001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A169">
-        <v>2026</v>
-      </c>
-      <c r="B169" t="s">
-        <v>13</v>
-      </c>
-      <c r="C169">
-        <v>16736361</v>
-      </c>
-      <c r="D169">
-        <v>1798.7820099999999</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A170">
-        <v>2027</v>
-      </c>
-      <c r="B170" t="s">
-        <v>7</v>
-      </c>
-      <c r="C170">
-        <v>51043704</v>
-      </c>
-      <c r="D170">
-        <v>3248.7946830000001</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A171">
-        <v>2027</v>
-      </c>
-      <c r="B171" t="s">
-        <v>8</v>
-      </c>
-      <c r="C171">
-        <v>100140559</v>
-      </c>
-      <c r="D171">
-        <v>12906.282364000001</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A172">
-        <v>2027</v>
-      </c>
-      <c r="B172" t="s">
-        <v>9</v>
-      </c>
-      <c r="C172">
-        <v>468895</v>
-      </c>
-      <c r="D172">
-        <v>26.192430999999999</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A173">
-        <v>2027</v>
-      </c>
-      <c r="B173" t="s">
-        <v>10</v>
-      </c>
-      <c r="C173">
-        <v>10624007</v>
-      </c>
-      <c r="D173">
-        <v>1278.9460220000001</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A174">
-        <v>2027</v>
-      </c>
-      <c r="B174" t="s">
-        <v>11</v>
-      </c>
-      <c r="C174">
-        <v>36653386</v>
-      </c>
-      <c r="D174">
-        <v>315.75279999999998</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A175">
-        <v>2027</v>
-      </c>
-      <c r="B175" t="s">
-        <v>12</v>
-      </c>
-      <c r="C175">
-        <v>12812040</v>
-      </c>
-      <c r="D175">
-        <v>2024.2953189999998</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A176">
-        <v>2027</v>
-      </c>
-      <c r="B176" t="s">
-        <v>13</v>
-      </c>
-      <c r="C176">
-        <v>4229762</v>
-      </c>
-      <c r="D176">
         <v>573.08676000000003</v>
       </c>
     </row>
